--- a/internal_doc/00.项目管理/00.任务计划/对外文档规划表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/对外文档规划表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="45" windowWidth="19920" windowHeight="7815"/>
+    <workbookView xWindow="360" yWindow="45" windowWidth="19920" windowHeight="7815" tabRatio="409"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -667,20 +667,134 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.24994659260841701"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -689,11 +803,56 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -990,1138 +1149,2059 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J120"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:J122"/>
+  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="13.75" customWidth="1"/>
-    <col min="2" max="2" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48.5" customWidth="1"/>
     <col min="5" max="5" width="15.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="93.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="B3" t="s">
+    <row r="3" spans="1:10" outlineLevel="1">
+      <c r="A3" s="5"/>
+      <c r="B3" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="67.5">
-      <c r="C4" t="s">
+    <row r="4" spans="1:10" ht="67.5" outlineLevel="2">
+      <c r="A4" s="5"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="13">
         <v>8</v>
       </c>
-      <c r="G4">
+      <c r="F4" s="13"/>
+      <c r="G4" s="13">
         <v>10000</v>
       </c>
-      <c r="J4" t="s">
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="67.5">
-      <c r="C5" t="s">
+    <row r="5" spans="1:10" ht="67.5" outlineLevel="2">
+      <c r="A5" s="5"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="13">
         <v>4</v>
       </c>
-      <c r="G5">
+      <c r="F5" s="13"/>
+      <c r="G5" s="13">
         <v>5000</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="54">
-      <c r="C6" t="s">
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+    </row>
+    <row r="6" spans="1:10" ht="54" outlineLevel="2">
+      <c r="A6" s="5"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="13">
         <v>7</v>
       </c>
-      <c r="G6">
+      <c r="F6" s="13"/>
+      <c r="G6" s="13">
         <v>8000</v>
       </c>
-      <c r="J6" t="s">
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="67.5">
-      <c r="C7" t="s">
+    <row r="7" spans="1:10" ht="67.5" outlineLevel="2">
+      <c r="A7" s="5"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="13">
         <v>7</v>
       </c>
-      <c r="G7">
+      <c r="F7" s="13"/>
+      <c r="G7" s="13">
         <v>5000</v>
       </c>
-      <c r="J7" t="s">
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="67.5">
-      <c r="C8" t="s">
+    <row r="8" spans="1:10" ht="67.5" outlineLevel="2">
+      <c r="A8" s="5"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="13">
         <v>7</v>
       </c>
-      <c r="G8">
+      <c r="F8" s="13"/>
+      <c r="G8" s="13">
         <v>20000</v>
       </c>
-      <c r="J8" t="s">
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="54">
-      <c r="C9" t="s">
+    <row r="9" spans="1:10" ht="54" outlineLevel="2">
+      <c r="A9" s="5"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="13">
         <v>5</v>
       </c>
-      <c r="G9">
+      <c r="F9" s="13"/>
+      <c r="G9" s="13">
         <v>5000</v>
       </c>
-      <c r="J9" t="s">
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="40.5">
-      <c r="C10" t="s">
+    <row r="10" spans="1:10" ht="40.5" outlineLevel="2">
+      <c r="A10" s="5"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="13">
         <v>6</v>
       </c>
-      <c r="G10">
+      <c r="F10" s="13"/>
+      <c r="G10" s="13">
         <v>8000</v>
       </c>
-      <c r="J10" t="s">
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="B11" t="s">
+    <row r="11" spans="1:10" outlineLevel="1">
+      <c r="A11" s="5"/>
+      <c r="B11" s="11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="40.5">
-      <c r="C12" t="s">
+      <c r="C11" s="14"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10" ht="40.5" outlineLevel="2">
+      <c r="A12" s="5"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="13">
         <v>8</v>
       </c>
-      <c r="G12">
+      <c r="F12" s="13"/>
+      <c r="G12" s="13">
         <v>1500</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="27">
-      <c r="C13" t="s">
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" spans="1:10" ht="27" outlineLevel="2">
+      <c r="A13" s="5"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="13">
         <v>8</v>
       </c>
-      <c r="G13">
+      <c r="F13" s="13"/>
+      <c r="G13" s="13">
         <v>20000</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="40.5">
-      <c r="C14" t="s">
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+    </row>
+    <row r="14" spans="1:10" ht="40.5" outlineLevel="2">
+      <c r="A14" s="5"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="13">
         <v>8</v>
       </c>
-      <c r="G14">
+      <c r="F14" s="13"/>
+      <c r="G14" s="13">
         <v>20000</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="C15" t="s">
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="15" spans="1:10" outlineLevel="2">
+      <c r="A15" s="5"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="13">
         <v>8</v>
       </c>
-      <c r="G15">
+      <c r="F15" s="13"/>
+      <c r="G15" s="13">
         <v>5000</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="C16" t="s">
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="1:10" outlineLevel="2">
+      <c r="A16" s="5"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="13">
         <v>8</v>
       </c>
-      <c r="G16">
+      <c r="F16" s="13"/>
+      <c r="G16" s="13">
         <v>5000</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="B17" t="s">
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="1:10" outlineLevel="1">
+      <c r="A17" s="5"/>
+      <c r="B17" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="14" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="B18" t="s">
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+    </row>
+    <row r="18" spans="1:10" outlineLevel="1">
+      <c r="A18" s="6"/>
+      <c r="B18" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="14" t="s">
         <v>61</v>
       </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" t="s">
+      <c r="A19" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="40.5">
-      <c r="B20" t="s">
+      <c r="C19" s="14"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+    </row>
+    <row r="20" spans="1:10" ht="40.5" outlineLevel="1">
+      <c r="A20" s="5"/>
+      <c r="B20" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="13">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="C21" t="s">
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" spans="1:10" outlineLevel="2">
+      <c r="A21" s="5"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G21">
-        <v>1000</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
-      <c r="C22" t="s">
+    <row r="22" spans="1:10" outlineLevel="2">
+      <c r="A22" s="5"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G22">
-        <v>1000</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
-      <c r="C23" t="s">
+    <row r="23" spans="1:10" outlineLevel="2">
+      <c r="A23" s="5"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G23">
-        <v>1000</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
-      <c r="C24" t="s">
+    <row r="24" spans="1:10" outlineLevel="2">
+      <c r="A24" s="5"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G24">
-        <v>1000</v>
-      </c>
-      <c r="J24" t="s">
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
-      <c r="C25" t="s">
+    <row r="25" spans="1:10" outlineLevel="2">
+      <c r="A25" s="5"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="G25">
-        <v>1000</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
-      <c r="C26" t="s">
+    <row r="26" spans="1:10" outlineLevel="2">
+      <c r="A26" s="5"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="G26">
-        <v>1000</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="27">
-      <c r="B27" t="s">
+    <row r="27" spans="1:10" ht="27" outlineLevel="1">
+      <c r="A27" s="5"/>
+      <c r="B27" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E27">
+      <c r="D27" s="13"/>
+      <c r="E27" s="13">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="C28" t="s">
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+    </row>
+    <row r="28" spans="1:10" outlineLevel="2">
+      <c r="A28" s="5"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G28">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="C29" t="s">
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+    </row>
+    <row r="29" spans="1:10" outlineLevel="2">
+      <c r="A29" s="5"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="G29">
-        <v>1000</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="C30" t="s">
+    <row r="30" spans="1:10" outlineLevel="2">
+      <c r="A30" s="5"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G30">
-        <v>1000</v>
-      </c>
-      <c r="J30" t="s">
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="C31" t="s">
+    <row r="31" spans="1:10" outlineLevel="2">
+      <c r="A31" s="5"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="G31">
-        <v>1000</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
-      <c r="C32" t="s">
+    <row r="32" spans="1:10" outlineLevel="2">
+      <c r="A32" s="5"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G32">
-        <v>1000</v>
-      </c>
-      <c r="J32" t="s">
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
-      <c r="C33" t="s">
+    <row r="33" spans="1:10" outlineLevel="2">
+      <c r="A33" s="5"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G33">
-        <v>1000</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
-      <c r="B34" t="s">
+    <row r="34" spans="1:10" outlineLevel="1">
+      <c r="A34" s="5"/>
+      <c r="B34" s="11" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="C35" t="s">
+      <c r="C34" s="14"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+    </row>
+    <row r="35" spans="1:10" outlineLevel="2">
+      <c r="A35" s="5"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="E35">
+      <c r="D35" s="13"/>
+      <c r="E35" s="13">
         <v>5</v>
       </c>
-      <c r="G35">
+      <c r="F35" s="13"/>
+      <c r="G35" s="13">
         <v>2000</v>
       </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="C36" t="s">
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+    </row>
+    <row r="36" spans="1:10" outlineLevel="2">
+      <c r="A36" s="5"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E36">
+      <c r="D36" s="13"/>
+      <c r="E36" s="13">
+        <v>6</v>
+      </c>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+    </row>
+    <row r="37" spans="1:10" outlineLevel="2">
+      <c r="A37" s="5"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13">
+        <v>6</v>
+      </c>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13">
+        <v>1500</v>
+      </c>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+    </row>
+    <row r="38" spans="1:10" outlineLevel="2">
+      <c r="A38" s="5"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13">
+        <v>6</v>
+      </c>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13">
+        <v>1500</v>
+      </c>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+    </row>
+    <row r="39" spans="1:10" outlineLevel="2">
+      <c r="A39" s="5"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13">
+        <v>6</v>
+      </c>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+    </row>
+    <row r="40" spans="1:10" outlineLevel="2">
+      <c r="A40" s="5"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13">
+        <v>4</v>
+      </c>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13">
+        <v>1500</v>
+      </c>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" spans="1:10" outlineLevel="2">
+      <c r="A41" s="5"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="1:10" outlineLevel="1">
+      <c r="A42" s="5"/>
+      <c r="B42" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="14"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+    </row>
+    <row r="43" spans="1:10" outlineLevel="2">
+      <c r="A43" s="5"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13">
         <v>8</v>
       </c>
-      <c r="G36">
+      <c r="F43" s="13"/>
+      <c r="G43" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+    </row>
+    <row r="44" spans="1:10" outlineLevel="2">
+      <c r="A44" s="5"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13">
+        <v>8</v>
+      </c>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+    </row>
+    <row r="45" spans="1:10" outlineLevel="2">
+      <c r="A45" s="5"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+    </row>
+    <row r="46" spans="1:10" outlineLevel="1">
+      <c r="A46" s="5"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+    </row>
+    <row r="47" spans="1:10" outlineLevel="1">
+      <c r="A47" s="6"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="14"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+    </row>
+    <row r="49" spans="1:10" outlineLevel="1">
+      <c r="A49" s="5"/>
+      <c r="B49" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" s="14"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+    </row>
+    <row r="50" spans="1:10" outlineLevel="2">
+      <c r="A50" s="5"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13">
+        <v>5</v>
+      </c>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+    </row>
+    <row r="51" spans="1:10" outlineLevel="2">
+      <c r="A51" s="5"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13">
+        <v>5</v>
+      </c>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13">
+        <v>3000</v>
+      </c>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="1:10" outlineLevel="2">
+      <c r="A52" s="5"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13">
+        <v>5</v>
+      </c>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13">
+        <v>3000</v>
+      </c>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+    </row>
+    <row r="53" spans="1:10" outlineLevel="2">
+      <c r="A53" s="5"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13">
+        <v>5</v>
+      </c>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
+    </row>
+    <row r="54" spans="1:10" outlineLevel="2">
+      <c r="A54" s="5"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13">
+        <v>5</v>
+      </c>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+    </row>
+    <row r="55" spans="1:10" outlineLevel="1">
+      <c r="A55" s="5"/>
+      <c r="B55" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" s="14"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+    </row>
+    <row r="56" spans="1:10" outlineLevel="2">
+      <c r="A56" s="5"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13">
+        <v>5</v>
+      </c>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+    </row>
+    <row r="57" spans="1:10" outlineLevel="2">
+      <c r="A57" s="5"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13">
+        <v>5</v>
+      </c>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+    </row>
+    <row r="58" spans="1:10" outlineLevel="2">
+      <c r="A58" s="5"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13">
+        <v>3</v>
+      </c>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+    </row>
+    <row r="59" spans="1:10" outlineLevel="2">
+      <c r="A59" s="5"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13">
+        <v>1</v>
+      </c>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+    </row>
+    <row r="60" spans="1:10" outlineLevel="1">
+      <c r="A60" s="5"/>
+      <c r="B60" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="14"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+    </row>
+    <row r="61" spans="1:10" outlineLevel="2">
+      <c r="A61" s="5"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13">
+        <v>6</v>
+      </c>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+    </row>
+    <row r="62" spans="1:10" outlineLevel="2">
+      <c r="A62" s="5"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13">
+        <v>5</v>
+      </c>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+    </row>
+    <row r="63" spans="1:10" outlineLevel="2">
+      <c r="A63" s="5"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13">
+        <v>6</v>
+      </c>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
+    </row>
+    <row r="64" spans="1:10" outlineLevel="2">
+      <c r="A64" s="5"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13">
+        <v>6</v>
+      </c>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
+    </row>
+    <row r="65" spans="1:10" outlineLevel="2">
+      <c r="A65" s="5"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13">
+        <v>5</v>
+      </c>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+    </row>
+    <row r="66" spans="1:10" outlineLevel="2">
+      <c r="A66" s="5"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+    </row>
+    <row r="67" spans="1:10" outlineLevel="1">
+      <c r="A67" s="5"/>
+      <c r="B67" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C67" s="14"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+    </row>
+    <row r="68" spans="1:10" outlineLevel="2">
+      <c r="A68" s="5"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13">
+        <v>5</v>
+      </c>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="1:10" outlineLevel="2">
+      <c r="A69" s="5"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13">
+        <v>5</v>
+      </c>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+    </row>
+    <row r="70" spans="1:10" outlineLevel="2">
+      <c r="A70" s="5"/>
+      <c r="B70" s="10"/>
+      <c r="C70" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13">
+        <v>4</v>
+      </c>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+    </row>
+    <row r="71" spans="1:10" outlineLevel="1">
+      <c r="A71" s="5"/>
+      <c r="B71" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C71" s="14"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+    </row>
+    <row r="72" spans="1:10" outlineLevel="2">
+      <c r="A72" s="5"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13">
+        <v>5</v>
+      </c>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13">
         <v>2000</v>
       </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="C37" t="s">
-        <v>82</v>
-      </c>
-      <c r="E37">
-        <v>8</v>
-      </c>
-      <c r="G37">
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
+    </row>
+    <row r="73" spans="1:10" outlineLevel="2">
+      <c r="A73" s="5"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13">
+        <v>4</v>
+      </c>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
+    </row>
+    <row r="74" spans="1:10" outlineLevel="2">
+      <c r="A74" s="5"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13">
+        <v>5</v>
+      </c>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
+    </row>
+    <row r="75" spans="1:10" outlineLevel="2">
+      <c r="A75" s="5"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13">
+        <v>5</v>
+      </c>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13">
+        <v>3000</v>
+      </c>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
+    </row>
+    <row r="76" spans="1:10" outlineLevel="2">
+      <c r="A76" s="5"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13">
+        <v>3</v>
+      </c>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="13"/>
+    </row>
+    <row r="77" spans="1:10" outlineLevel="2">
+      <c r="A77" s="5"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13">
+        <v>3</v>
+      </c>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
+    </row>
+    <row r="78" spans="1:10" outlineLevel="2">
+      <c r="A78" s="5"/>
+      <c r="B78" s="10"/>
+      <c r="C78" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13">
+        <v>5</v>
+      </c>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13">
+        <v>3000</v>
+      </c>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="13"/>
+    </row>
+    <row r="79" spans="1:10" outlineLevel="1">
+      <c r="A79" s="5"/>
+      <c r="B79" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C79" s="14"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="13"/>
+    </row>
+    <row r="80" spans="1:10" outlineLevel="2">
+      <c r="A80" s="5"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13">
+        <v>5</v>
+      </c>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
+      <c r="J80" s="13"/>
+    </row>
+    <row r="81" spans="1:10" outlineLevel="2">
+      <c r="A81" s="5"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13">
+        <v>5</v>
+      </c>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13">
         <v>1500</v>
       </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="C38" t="s">
-        <v>83</v>
-      </c>
-      <c r="E38">
-        <v>8</v>
-      </c>
-      <c r="G38">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="C39" t="s">
-        <v>86</v>
-      </c>
-      <c r="E39">
-        <v>8</v>
-      </c>
-      <c r="G39">
+      <c r="H81" s="13"/>
+      <c r="I81" s="13"/>
+      <c r="J81" s="13"/>
+    </row>
+    <row r="82" spans="1:10" outlineLevel="2">
+      <c r="A82" s="5"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13">
+        <v>3</v>
+      </c>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13">
+        <v>3000</v>
+      </c>
+      <c r="H82" s="13"/>
+      <c r="I82" s="13"/>
+      <c r="J82" s="13"/>
+    </row>
+    <row r="83" spans="1:10" outlineLevel="2">
+      <c r="A83" s="5"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13">
+        <v>6</v>
+      </c>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H83" s="13"/>
+      <c r="I83" s="13"/>
+      <c r="J83" s="13"/>
+    </row>
+    <row r="84" spans="1:10" outlineLevel="2">
+      <c r="A84" s="5"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13">
+        <v>6</v>
+      </c>
+      <c r="F84" s="13"/>
+      <c r="G84" s="13">
+        <v>3000</v>
+      </c>
+      <c r="H84" s="13"/>
+      <c r="I84" s="13"/>
+      <c r="J84" s="13"/>
+    </row>
+    <row r="85" spans="1:10" outlineLevel="2">
+      <c r="A85" s="5"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13">
+        <v>4</v>
+      </c>
+      <c r="F85" s="13"/>
+      <c r="G85" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H85" s="13"/>
+      <c r="I85" s="13"/>
+      <c r="J85" s="13"/>
+    </row>
+    <row r="86" spans="1:10" ht="11.25" customHeight="1" outlineLevel="1">
+      <c r="A86" s="5"/>
+      <c r="B86" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C86" s="14"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
+      <c r="J86" s="13"/>
+    </row>
+    <row r="87" spans="1:10" outlineLevel="2">
+      <c r="A87" s="5"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13">
+        <v>5</v>
+      </c>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13">
         <v>2000</v>
       </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="C40" t="s">
-        <v>85</v>
-      </c>
-      <c r="E40">
+      <c r="H87" s="13"/>
+      <c r="I87" s="13"/>
+      <c r="J87" s="13"/>
+    </row>
+    <row r="88" spans="1:10" outlineLevel="2">
+      <c r="A88" s="5"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D88" s="13"/>
+      <c r="E88" s="13">
+        <v>5</v>
+      </c>
+      <c r="F88" s="13"/>
+      <c r="G88" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H88" s="13"/>
+      <c r="I88" s="13"/>
+      <c r="J88" s="13"/>
+    </row>
+    <row r="89" spans="1:10" outlineLevel="2">
+      <c r="A89" s="5"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13">
+        <v>5</v>
+      </c>
+      <c r="F89" s="13"/>
+      <c r="G89" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13"/>
+      <c r="J89" s="13"/>
+    </row>
+    <row r="90" spans="1:10" outlineLevel="2">
+      <c r="A90" s="5"/>
+      <c r="B90" s="10"/>
+      <c r="C90" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13">
+        <v>5</v>
+      </c>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="13"/>
+    </row>
+    <row r="91" spans="1:10" outlineLevel="1">
+      <c r="A91" s="5"/>
+      <c r="B91" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C91" s="14"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="13"/>
+      <c r="H91" s="13"/>
+      <c r="I91" s="13"/>
+      <c r="J91" s="13"/>
+    </row>
+    <row r="92" spans="1:10" outlineLevel="2">
+      <c r="A92" s="5"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="D92" s="13"/>
+      <c r="E92" s="13">
+        <v>5</v>
+      </c>
+      <c r="F92" s="13"/>
+      <c r="G92" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H92" s="13"/>
+      <c r="I92" s="13"/>
+      <c r="J92" s="13"/>
+    </row>
+    <row r="93" spans="1:10" outlineLevel="2">
+      <c r="A93" s="5"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13">
+        <v>5</v>
+      </c>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H93" s="13"/>
+      <c r="I93" s="13"/>
+      <c r="J93" s="13"/>
+    </row>
+    <row r="94" spans="1:10" outlineLevel="2">
+      <c r="A94" s="5"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13">
+        <v>5</v>
+      </c>
+      <c r="F94" s="13"/>
+      <c r="G94" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H94" s="13"/>
+      <c r="I94" s="13"/>
+      <c r="J94" s="13"/>
+    </row>
+    <row r="95" spans="1:10" outlineLevel="2">
+      <c r="A95" s="5"/>
+      <c r="B95" s="10"/>
+      <c r="C95" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D95" s="13"/>
+      <c r="E95" s="13">
+        <v>5</v>
+      </c>
+      <c r="F95" s="13"/>
+      <c r="G95" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H95" s="13"/>
+      <c r="I95" s="13"/>
+      <c r="J95" s="13"/>
+    </row>
+    <row r="96" spans="1:10" outlineLevel="1">
+      <c r="A96" s="5"/>
+      <c r="B96" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C96" s="14"/>
+      <c r="D96" s="13"/>
+      <c r="E96" s="13"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13"/>
+      <c r="I96" s="13"/>
+      <c r="J96" s="13"/>
+    </row>
+    <row r="97" spans="1:10" outlineLevel="2">
+      <c r="A97" s="5"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D97" s="13"/>
+      <c r="E97" s="13">
         <v>4</v>
       </c>
-      <c r="G40">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="B42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="C43" t="s">
-        <v>87</v>
-      </c>
-      <c r="E43">
-        <v>8</v>
-      </c>
-      <c r="G43">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="C44" t="s">
-        <v>88</v>
-      </c>
-      <c r="E44">
-        <v>8</v>
-      </c>
-      <c r="G44">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7">
-      <c r="B49" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7">
-      <c r="C50" t="s">
-        <v>111</v>
-      </c>
-      <c r="E50">
-        <v>5</v>
-      </c>
-      <c r="G50">
+      <c r="F97" s="13"/>
+      <c r="G97" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H97" s="13"/>
+      <c r="I97" s="13"/>
+      <c r="J97" s="13"/>
+    </row>
+    <row r="98" spans="1:10" outlineLevel="2">
+      <c r="A98" s="5"/>
+      <c r="B98" s="10"/>
+      <c r="C98" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D98" s="13"/>
+      <c r="E98" s="13">
+        <v>4</v>
+      </c>
+      <c r="F98" s="13"/>
+      <c r="G98" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H98" s="13"/>
+      <c r="I98" s="13"/>
+      <c r="J98" s="13"/>
+    </row>
+    <row r="99" spans="1:10" outlineLevel="1">
+      <c r="A99" s="5"/>
+      <c r="B99" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C99" s="14"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13"/>
+      <c r="H99" s="13"/>
+      <c r="I99" s="13"/>
+      <c r="J99" s="13"/>
+    </row>
+    <row r="100" spans="1:10" outlineLevel="2">
+      <c r="A100" s="5"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13">
+        <v>4</v>
+      </c>
+      <c r="F100" s="13"/>
+      <c r="G100" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H100" s="13"/>
+      <c r="I100" s="13"/>
+      <c r="J100" s="13"/>
+    </row>
+    <row r="101" spans="1:10" outlineLevel="2">
+      <c r="A101" s="5"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D101" s="13"/>
+      <c r="E101" s="13">
+        <v>4</v>
+      </c>
+      <c r="F101" s="13"/>
+      <c r="G101" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H101" s="13"/>
+      <c r="I101" s="13"/>
+      <c r="J101" s="13"/>
+    </row>
+    <row r="102" spans="1:10" outlineLevel="2">
+      <c r="A102" s="6"/>
+      <c r="B102" s="10"/>
+      <c r="C102" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D102" s="13"/>
+      <c r="E102" s="13">
+        <v>4</v>
+      </c>
+      <c r="F102" s="13"/>
+      <c r="G102" s="13">
         <v>5000</v>
       </c>
-    </row>
-    <row r="51" spans="2:7">
-      <c r="C51" t="s">
-        <v>112</v>
-      </c>
-      <c r="E51">
-        <v>5</v>
-      </c>
-      <c r="G51">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7">
-      <c r="C52" t="s">
-        <v>113</v>
-      </c>
-      <c r="E52">
-        <v>5</v>
-      </c>
-      <c r="G52">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7">
-      <c r="C53" t="s">
-        <v>114</v>
-      </c>
-      <c r="E53">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7">
-      <c r="C54" t="s">
-        <v>115</v>
-      </c>
-      <c r="E54">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7">
-      <c r="B55" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7">
-      <c r="C56" t="s">
-        <v>117</v>
-      </c>
-      <c r="E56">
-        <v>5</v>
-      </c>
-      <c r="G56">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7">
-      <c r="C57" t="s">
-        <v>118</v>
-      </c>
-      <c r="E57">
-        <v>5</v>
-      </c>
-      <c r="G57">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7">
-      <c r="C58" t="s">
-        <v>119</v>
-      </c>
-      <c r="E58">
-        <v>3</v>
-      </c>
-      <c r="G58">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7">
-      <c r="C59" t="s">
-        <v>120</v>
-      </c>
-      <c r="E59">
-        <v>1</v>
-      </c>
-      <c r="G59">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7">
-      <c r="B60" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7">
-      <c r="C61" t="s">
-        <v>99</v>
-      </c>
-      <c r="E61">
-        <v>6</v>
-      </c>
-      <c r="G61">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7">
-      <c r="C62" t="s">
-        <v>100</v>
-      </c>
-      <c r="E62">
-        <v>5</v>
-      </c>
-      <c r="G62">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7">
-      <c r="C63" t="s">
-        <v>101</v>
-      </c>
-      <c r="E63">
-        <v>6</v>
-      </c>
-      <c r="G63">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7">
-      <c r="C64" t="s">
-        <v>102</v>
-      </c>
-      <c r="E64">
-        <v>6</v>
-      </c>
-      <c r="G64">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7">
-      <c r="C65" t="s">
-        <v>103</v>
-      </c>
-      <c r="E65">
-        <v>5</v>
-      </c>
-      <c r="G65">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7">
-      <c r="B67" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="68" spans="2:7">
-      <c r="C68" t="s">
-        <v>107</v>
-      </c>
-      <c r="E68">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="2:7">
-      <c r="C69" t="s">
-        <v>106</v>
-      </c>
-      <c r="E69">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="2:7">
-      <c r="C70" t="s">
-        <v>105</v>
-      </c>
-      <c r="E70">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="2:7">
-      <c r="B71" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="72" spans="2:7">
-      <c r="C72" t="s">
-        <v>108</v>
-      </c>
-      <c r="E72">
-        <v>5</v>
-      </c>
-      <c r="G72">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="73" spans="2:7">
-      <c r="C73" t="s">
-        <v>109</v>
-      </c>
-      <c r="E73">
-        <v>4</v>
-      </c>
-      <c r="G73">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="74" spans="2:7">
-      <c r="C74" t="s">
-        <v>121</v>
-      </c>
-      <c r="E74">
-        <v>5</v>
-      </c>
-      <c r="G74">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="75" spans="2:7">
-      <c r="C75" t="s">
-        <v>122</v>
-      </c>
-      <c r="E75">
-        <v>5</v>
-      </c>
-      <c r="G75">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="76" spans="2:7">
-      <c r="C76" t="s">
-        <v>123</v>
-      </c>
-      <c r="E76">
-        <v>3</v>
-      </c>
-      <c r="G76">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="77" spans="2:7">
-      <c r="C77" t="s">
-        <v>125</v>
-      </c>
-      <c r="E77">
-        <v>3</v>
-      </c>
-      <c r="G77">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="78" spans="2:7">
-      <c r="C78" t="s">
-        <v>131</v>
-      </c>
-      <c r="E78">
-        <v>5</v>
-      </c>
-      <c r="G78">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="79" spans="2:7">
-      <c r="B79" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="80" spans="2:7">
-      <c r="C80" t="s">
-        <v>126</v>
-      </c>
-      <c r="E80">
-        <v>5</v>
-      </c>
-      <c r="G80">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="81" spans="2:7">
-      <c r="C81" t="s">
-        <v>127</v>
-      </c>
-      <c r="E81">
-        <v>5</v>
-      </c>
-      <c r="G81">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7">
-      <c r="C82" t="s">
-        <v>128</v>
-      </c>
-      <c r="E82">
-        <v>3</v>
-      </c>
-      <c r="G82">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="83" spans="2:7">
-      <c r="C83" t="s">
-        <v>129</v>
-      </c>
-      <c r="E83">
-        <v>6</v>
-      </c>
-      <c r="G83">
+      <c r="H102" s="13"/>
+      <c r="I102" s="13"/>
+      <c r="J102" s="13"/>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C103" s="14"/>
+      <c r="D103" s="13"/>
+      <c r="E103" s="13"/>
+      <c r="F103" s="13"/>
+      <c r="G103" s="13"/>
+      <c r="H103" s="13"/>
+      <c r="I103" s="13"/>
+      <c r="J103" s="13"/>
+    </row>
+    <row r="104" spans="1:10" outlineLevel="1">
+      <c r="A104" s="5"/>
+      <c r="B104" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C104" s="14"/>
+      <c r="D104" s="13"/>
+      <c r="E104" s="13">
+        <v>7</v>
+      </c>
+      <c r="F104" s="13"/>
+      <c r="G104" s="13">
         <v>5000</v>
       </c>
-    </row>
-    <row r="84" spans="2:7">
-      <c r="C84" t="s">
-        <v>130</v>
-      </c>
-      <c r="E84">
-        <v>6</v>
-      </c>
-      <c r="G84">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="85" spans="2:7">
-      <c r="C85" t="s">
-        <v>132</v>
-      </c>
-      <c r="E85">
-        <v>4</v>
-      </c>
-      <c r="G85">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7">
-      <c r="B86" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="87" spans="2:7">
-      <c r="C87" t="s">
-        <v>134</v>
-      </c>
-      <c r="E87">
-        <v>5</v>
-      </c>
-      <c r="G87">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7">
-      <c r="C88" t="s">
-        <v>135</v>
-      </c>
-      <c r="E88">
-        <v>5</v>
-      </c>
-      <c r="G88">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="89" spans="2:7">
-      <c r="C89" t="s">
-        <v>136</v>
-      </c>
-      <c r="E89">
-        <v>5</v>
-      </c>
-      <c r="G89">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7">
-      <c r="C90" t="s">
-        <v>137</v>
-      </c>
-      <c r="E90">
-        <v>5</v>
-      </c>
-      <c r="G90">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7">
-      <c r="B91" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="92" spans="2:7">
-      <c r="C92" t="s">
-        <v>138</v>
-      </c>
-      <c r="E92">
-        <v>5</v>
-      </c>
-      <c r="G92">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7">
-      <c r="C93" t="s">
-        <v>139</v>
-      </c>
-      <c r="E93">
-        <v>5</v>
-      </c>
-      <c r="G93">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7">
-      <c r="C94" t="s">
-        <v>140</v>
-      </c>
-      <c r="E94">
-        <v>5</v>
-      </c>
-      <c r="G94">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7">
-      <c r="C95" t="s">
-        <v>141</v>
-      </c>
-      <c r="E95">
-        <v>5</v>
-      </c>
-      <c r="G95">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7">
-      <c r="B96" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="C97" t="s">
-        <v>142</v>
-      </c>
-      <c r="E97">
-        <v>4</v>
-      </c>
-      <c r="G97">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="C98" t="s">
-        <v>143</v>
-      </c>
-      <c r="E98">
-        <v>4</v>
-      </c>
-      <c r="G98">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="B99" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="C100" t="s">
-        <v>144</v>
-      </c>
-      <c r="E100">
-        <v>4</v>
-      </c>
-      <c r="G100">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="C101" t="s">
-        <v>145</v>
-      </c>
-      <c r="E101">
-        <v>4</v>
-      </c>
-      <c r="G101">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="C102" t="s">
-        <v>146</v>
-      </c>
-      <c r="E102">
-        <v>4</v>
-      </c>
-      <c r="G102">
+      <c r="H104" s="13"/>
+      <c r="I104" s="13"/>
+      <c r="J104" s="13"/>
+    </row>
+    <row r="105" spans="1:10" outlineLevel="1">
+      <c r="A105" s="5"/>
+      <c r="B105" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C105" s="14"/>
+      <c r="D105" s="13"/>
+      <c r="E105" s="13">
+        <v>7</v>
+      </c>
+      <c r="F105" s="13"/>
+      <c r="G105" s="13">
         <v>5000</v>
       </c>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="A103" t="s">
-        <v>11</v>
-      </c>
-      <c r="B103" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
-      <c r="B104" t="s">
-        <v>47</v>
-      </c>
-      <c r="E104">
+      <c r="H105" s="13"/>
+      <c r="I105" s="13"/>
+      <c r="J105" s="13"/>
+    </row>
+    <row r="106" spans="1:10" outlineLevel="1">
+      <c r="A106" s="5"/>
+      <c r="B106" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C106" s="14"/>
+      <c r="D106" s="13"/>
+      <c r="E106" s="13">
         <v>7</v>
       </c>
-      <c r="G104">
+      <c r="F106" s="13"/>
+      <c r="G106" s="13">
         <v>5000</v>
       </c>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="B105" t="s">
-        <v>46</v>
-      </c>
-      <c r="E105">
+      <c r="H106" s="13"/>
+      <c r="I106" s="13"/>
+      <c r="J106" s="13"/>
+    </row>
+    <row r="107" spans="1:10" outlineLevel="1">
+      <c r="A107" s="5"/>
+      <c r="B107" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C107" s="14"/>
+      <c r="D107" s="13"/>
+      <c r="E107" s="13">
         <v>7</v>
       </c>
-      <c r="G105">
+      <c r="F107" s="13"/>
+      <c r="G107" s="13">
         <v>5000</v>
       </c>
-    </row>
-    <row r="106" spans="1:7">
-      <c r="B106" t="s">
-        <v>45</v>
-      </c>
-      <c r="E106">
-        <v>7</v>
-      </c>
-      <c r="G106">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
-      <c r="B107" t="s">
-        <v>44</v>
-      </c>
-      <c r="E107">
-        <v>7</v>
-      </c>
-      <c r="G107">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
-      <c r="A109" t="s">
+      <c r="H107" s="13"/>
+      <c r="I107" s="13"/>
+      <c r="J107" s="13"/>
+    </row>
+    <row r="108" spans="1:10" outlineLevel="1">
+      <c r="A108" s="6"/>
+      <c r="B108" s="10"/>
+      <c r="C108" s="14"/>
+      <c r="D108" s="13"/>
+      <c r="E108" s="13"/>
+      <c r="F108" s="13"/>
+      <c r="G108" s="13"/>
+      <c r="H108" s="13"/>
+      <c r="I108" s="13"/>
+      <c r="J108" s="13"/>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="110" spans="1:7">
-      <c r="B110" t="s">
+      <c r="C109" s="14"/>
+      <c r="D109" s="13"/>
+      <c r="E109" s="13"/>
+      <c r="F109" s="13"/>
+      <c r="G109" s="13"/>
+      <c r="H109" s="13"/>
+      <c r="I109" s="13"/>
+      <c r="J109" s="13"/>
+    </row>
+    <row r="110" spans="1:10" outlineLevel="1">
+      <c r="A110" s="5"/>
+      <c r="B110" s="11" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" t="s">
+      <c r="C110" s="14"/>
+      <c r="D110" s="13"/>
+      <c r="E110" s="13"/>
+      <c r="F110" s="13"/>
+      <c r="G110" s="13"/>
+      <c r="H110" s="13"/>
+      <c r="I110" s="13"/>
+      <c r="J110" s="13"/>
+    </row>
+    <row r="111" spans="1:10" outlineLevel="1">
+      <c r="A111" s="5"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="14"/>
+      <c r="D111" s="13"/>
+      <c r="E111" s="13"/>
+      <c r="F111" s="13"/>
+      <c r="G111" s="13"/>
+      <c r="H111" s="13"/>
+      <c r="I111" s="13"/>
+      <c r="J111" s="13"/>
+    </row>
+    <row r="112" spans="1:10" outlineLevel="1">
+      <c r="A112" s="5"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="14"/>
+      <c r="D112" s="13"/>
+      <c r="E112" s="13"/>
+      <c r="F112" s="13"/>
+      <c r="G112" s="13"/>
+      <c r="H112" s="13"/>
+      <c r="I112" s="13"/>
+      <c r="J112" s="13"/>
+    </row>
+    <row r="113" spans="1:10" outlineLevel="1">
+      <c r="A113" s="6"/>
+      <c r="B113" s="10"/>
+      <c r="C113" s="14"/>
+      <c r="D113" s="13"/>
+      <c r="E113" s="13"/>
+      <c r="F113" s="13"/>
+      <c r="G113" s="13"/>
+      <c r="H113" s="13"/>
+      <c r="I113" s="13"/>
+      <c r="J113" s="13"/>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="B115" t="s">
+      <c r="C114" s="14"/>
+      <c r="D114" s="13"/>
+      <c r="E114" s="13"/>
+      <c r="F114" s="13"/>
+      <c r="G114" s="13"/>
+      <c r="H114" s="13"/>
+      <c r="I114" s="13"/>
+      <c r="J114" s="13"/>
+    </row>
+    <row r="115" spans="1:10" outlineLevel="1">
+      <c r="A115" s="5"/>
+      <c r="B115" s="11" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="C116" t="s">
+      <c r="C115" s="14"/>
+      <c r="D115" s="13"/>
+      <c r="E115" s="13"/>
+      <c r="F115" s="13"/>
+      <c r="G115" s="13"/>
+      <c r="H115" s="13"/>
+      <c r="I115" s="13"/>
+      <c r="J115" s="13"/>
+    </row>
+    <row r="116" spans="1:10" outlineLevel="1">
+      <c r="A116" s="5"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="14" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="B117" t="s">
+      <c r="D116" s="13"/>
+      <c r="E116" s="13"/>
+      <c r="F116" s="13"/>
+      <c r="G116" s="13"/>
+      <c r="H116" s="13"/>
+      <c r="I116" s="13"/>
+      <c r="J116" s="13"/>
+    </row>
+    <row r="117" spans="1:10" outlineLevel="1">
+      <c r="A117" s="5"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="16" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="B118" t="s">
+      <c r="D117" s="13"/>
+      <c r="E117" s="13"/>
+      <c r="F117" s="13"/>
+      <c r="G117" s="13"/>
+      <c r="H117" s="13"/>
+      <c r="I117" s="13"/>
+      <c r="J117" s="13"/>
+    </row>
+    <row r="118" spans="1:10" outlineLevel="1">
+      <c r="A118" s="5"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="16" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="B119" t="s">
+      <c r="D118" s="13"/>
+      <c r="E118" s="13"/>
+      <c r="F118" s="13"/>
+      <c r="G118" s="13"/>
+      <c r="H118" s="13"/>
+      <c r="I118" s="13"/>
+      <c r="J118" s="13"/>
+    </row>
+    <row r="119" spans="1:10" outlineLevel="1">
+      <c r="A119" s="5"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="16" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="B120" t="s">
+      <c r="D119" s="13"/>
+      <c r="E119" s="13"/>
+      <c r="F119" s="13"/>
+      <c r="G119" s="13"/>
+      <c r="H119" s="13"/>
+      <c r="I119" s="13"/>
+      <c r="J119" s="13"/>
+    </row>
+    <row r="120" spans="1:10" outlineLevel="1">
+      <c r="A120" s="6"/>
+      <c r="B120" s="10"/>
+      <c r="C120" s="16" t="s">
         <v>153</v>
       </c>
+      <c r="D120" s="13"/>
+      <c r="E120" s="13"/>
+      <c r="F120" s="13"/>
+      <c r="G120" s="13"/>
+      <c r="H120" s="13"/>
+      <c r="I120" s="13"/>
+      <c r="J120" s="13"/>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="C121" s="14"/>
+      <c r="D121" s="13"/>
+      <c r="E121" s="13"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="13"/>
+      <c r="H121" s="13"/>
+      <c r="I121" s="13"/>
+      <c r="J121" s="13"/>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="C122" s="14"/>
+      <c r="D122" s="13"/>
+      <c r="E122" s="13"/>
+      <c r="F122" s="13"/>
+      <c r="G122" s="13"/>
+      <c r="H122" s="13"/>
+      <c r="I122" s="13"/>
+      <c r="J122" s="13"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/internal_doc/00.项目管理/00.任务计划/对外文档规划表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/对外文档规划表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="202">
   <si>
     <t>主分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -530,10 +530,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PostgreSQL联邦能开销</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>数据复制机制</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -644,6 +640,196 @@
   <si>
     <t>转载IBM/Oracle等企业动态</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pdf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>web</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>web</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他发布渠道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>软文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打压</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王涛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邱尚高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李建华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海南航空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5月15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20小时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5月17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5月9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40小时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5月23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10小时</t>
+  </si>
+  <si>
+    <t>10小时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5月16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5月30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8小时</t>
+  </si>
+  <si>
+    <t>8小时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9小时</t>
+  </si>
+  <si>
+    <t>11小时</t>
+  </si>
+  <si>
+    <t>12小时</t>
+  </si>
+  <si>
+    <t>24小时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24小时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6月6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6月6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4小时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32小时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6月18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16小时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6月13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简单测试开启事务和关闭事务的性能对比，以分区系统为主</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PostgreSQL联邦性能测评</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5月18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7月4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6月30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丁普升</t>
+  </si>
+  <si>
+    <t>丁普升</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉8小时
+邱尚高8小时
+丁普升16小时</t>
+  </si>
+  <si>
+    <t>许建辉，邱尚高，丁普升</t>
   </si>
 </sst>
 </file>
@@ -803,7 +989,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -854,6 +1040,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1149,20 +1344,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:K123"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="13.75" style="3" customWidth="1"/>
     <col min="2" max="2" width="13.875" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48.5" customWidth="1"/>
-    <col min="5" max="5" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="93.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="11" max="11" width="93.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1">
+    <row r="1" spans="1:11" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1191,21 +1387,24 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" outlineLevel="1">
+    <row r="3" spans="1:11" outlineLevel="1">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="67.5" outlineLevel="2">
+    <row r="4" spans="1:11" ht="67.5" outlineLevel="2">
       <c r="A4" s="5"/>
       <c r="B4" s="9"/>
       <c r="C4" s="14" t="s">
@@ -1217,17 +1416,26 @@
       <c r="E4" s="13">
         <v>8</v>
       </c>
-      <c r="F4" s="13"/>
+      <c r="F4" s="13" t="s">
+        <v>167</v>
+      </c>
       <c r="G4" s="13">
         <v>10000</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
+      <c r="H4" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="J4" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K4" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="67.5" outlineLevel="2">
+    <row r="5" spans="1:11" ht="67.5" outlineLevel="2">
       <c r="A5" s="5"/>
       <c r="B5" s="9"/>
       <c r="C5" s="14" t="s">
@@ -1239,15 +1447,24 @@
       <c r="E5" s="13">
         <v>4</v>
       </c>
-      <c r="F5" s="13"/>
+      <c r="F5" s="13" t="s">
+        <v>169</v>
+      </c>
       <c r="G5" s="13">
         <v>5000</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-    </row>
-    <row r="6" spans="1:10" ht="54" outlineLevel="2">
+      <c r="H5" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K5" s="13"/>
+    </row>
+    <row r="6" spans="1:11" ht="54" outlineLevel="2">
       <c r="A6" s="5"/>
       <c r="B6" s="9"/>
       <c r="C6" s="14" t="s">
@@ -1259,17 +1476,26 @@
       <c r="E6" s="13">
         <v>7</v>
       </c>
-      <c r="F6" s="13"/>
+      <c r="F6" s="13" t="s">
+        <v>170</v>
+      </c>
       <c r="G6" s="13">
         <v>8000</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
+      <c r="H6" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>162</v>
+      </c>
       <c r="J6" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K6" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="67.5" outlineLevel="2">
+    <row r="7" spans="1:11" ht="67.5" outlineLevel="2">
       <c r="A7" s="5"/>
       <c r="B7" s="9"/>
       <c r="C7" s="14" t="s">
@@ -1281,17 +1507,26 @@
       <c r="E7" s="13">
         <v>7</v>
       </c>
-      <c r="F7" s="13"/>
+      <c r="F7" s="13" t="s">
+        <v>170</v>
+      </c>
       <c r="G7" s="13">
         <v>5000</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="H7" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>163</v>
+      </c>
       <c r="J7" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K7" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="67.5" outlineLevel="2">
+    <row r="8" spans="1:11" ht="67.5" outlineLevel="2">
       <c r="A8" s="5"/>
       <c r="B8" s="9"/>
       <c r="C8" s="14" t="s">
@@ -1303,17 +1538,26 @@
       <c r="E8" s="13">
         <v>7</v>
       </c>
-      <c r="F8" s="13"/>
+      <c r="F8" s="13" t="s">
+        <v>173</v>
+      </c>
       <c r="G8" s="13">
         <v>20000</v>
       </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
+      <c r="H8" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>163</v>
+      </c>
       <c r="J8" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K8" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="54" outlineLevel="2">
+    <row r="9" spans="1:11" ht="54" outlineLevel="2">
       <c r="A9" s="5"/>
       <c r="B9" s="9"/>
       <c r="C9" s="14" t="s">
@@ -1325,17 +1569,26 @@
       <c r="E9" s="13">
         <v>5</v>
       </c>
-      <c r="F9" s="13"/>
+      <c r="F9" s="13" t="s">
+        <v>176</v>
+      </c>
       <c r="G9" s="13">
         <v>5000</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
+      <c r="H9" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>198</v>
+      </c>
       <c r="J9" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K9" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="40.5" outlineLevel="2">
+    <row r="10" spans="1:11" ht="40.5" outlineLevel="2">
       <c r="A10" s="5"/>
       <c r="B10" s="10"/>
       <c r="C10" s="14" t="s">
@@ -1347,17 +1600,26 @@
       <c r="E10" s="13">
         <v>6</v>
       </c>
-      <c r="F10" s="13"/>
+      <c r="F10" s="13" t="s">
+        <v>167</v>
+      </c>
       <c r="G10" s="13">
         <v>8000</v>
       </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
+      <c r="H10" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="J10" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K10" s="13" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:10" outlineLevel="1">
+    <row r="11" spans="1:11" outlineLevel="1">
       <c r="A11" s="5"/>
       <c r="B11" s="11" t="s">
         <v>49</v>
@@ -1370,8 +1632,9 @@
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
-    </row>
-    <row r="12" spans="1:10" ht="40.5" outlineLevel="2">
+      <c r="K11" s="13"/>
+    </row>
+    <row r="12" spans="1:11" ht="40.5" outlineLevel="2">
       <c r="A12" s="5"/>
       <c r="B12" s="9"/>
       <c r="C12" s="14" t="s">
@@ -1383,15 +1646,24 @@
       <c r="E12" s="13">
         <v>8</v>
       </c>
-      <c r="F12" s="13"/>
+      <c r="F12" s="13" t="s">
+        <v>165</v>
+      </c>
       <c r="G12" s="13">
         <v>1500</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-    </row>
-    <row r="13" spans="1:10" ht="27" outlineLevel="2">
+      <c r="H12" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K12" s="13"/>
+    </row>
+    <row r="13" spans="1:11" ht="27" outlineLevel="2">
       <c r="A13" s="5"/>
       <c r="B13" s="9"/>
       <c r="C13" s="14" t="s">
@@ -1403,15 +1675,24 @@
       <c r="E13" s="13">
         <v>8</v>
       </c>
-      <c r="F13" s="13"/>
+      <c r="F13" s="13" t="s">
+        <v>170</v>
+      </c>
       <c r="G13" s="13">
         <v>20000</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-    </row>
-    <row r="14" spans="1:10" ht="40.5" outlineLevel="2">
+      <c r="H13" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K13" s="13"/>
+    </row>
+    <row r="14" spans="1:11" ht="40.5" outlineLevel="2">
       <c r="A14" s="5"/>
       <c r="B14" s="9"/>
       <c r="C14" s="14" t="s">
@@ -1423,15 +1704,24 @@
       <c r="E14" s="13">
         <v>8</v>
       </c>
-      <c r="F14" s="13"/>
+      <c r="F14" s="13" t="s">
+        <v>170</v>
+      </c>
       <c r="G14" s="13">
         <v>20000</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-    </row>
-    <row r="15" spans="1:10" outlineLevel="2">
+      <c r="H14" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K14" s="13"/>
+    </row>
+    <row r="15" spans="1:11" outlineLevel="2">
       <c r="A15" s="5"/>
       <c r="B15" s="9"/>
       <c r="C15" s="14" t="s">
@@ -1443,15 +1733,24 @@
       <c r="E15" s="13">
         <v>8</v>
       </c>
-      <c r="F15" s="13"/>
+      <c r="F15" s="13" t="s">
+        <v>165</v>
+      </c>
       <c r="G15" s="13">
         <v>5000</v>
       </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-    </row>
-    <row r="16" spans="1:10" outlineLevel="2">
+      <c r="H15" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K15" s="13"/>
+    </row>
+    <row r="16" spans="1:11" ht="40.5" outlineLevel="2">
       <c r="A16" s="5"/>
       <c r="B16" s="9"/>
       <c r="C16" s="14" t="s">
@@ -1463,15 +1762,24 @@
       <c r="E16" s="13">
         <v>8</v>
       </c>
-      <c r="F16" s="13"/>
+      <c r="F16" s="14" t="s">
+        <v>200</v>
+      </c>
       <c r="G16" s="13">
         <v>5000</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-    </row>
-    <row r="17" spans="1:10" outlineLevel="1">
+      <c r="H16" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K16" s="13"/>
+    </row>
+    <row r="17" spans="1:11" outlineLevel="1">
       <c r="A17" s="5"/>
       <c r="B17" s="12" t="s">
         <v>59</v>
@@ -1486,8 +1794,9 @@
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
-    </row>
-    <row r="18" spans="1:10" outlineLevel="1">
+      <c r="K17" s="13"/>
+    </row>
+    <row r="18" spans="1:11" outlineLevel="1">
       <c r="A18" s="6"/>
       <c r="B18" s="12" t="s">
         <v>15</v>
@@ -1502,8 +1811,9 @@
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18" s="13"/>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="4" t="s">
         <v>9</v>
       </c>
@@ -1515,8 +1825,9 @@
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
-    </row>
-    <row r="20" spans="1:10" ht="40.5" outlineLevel="1">
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" ht="40.5" outlineLevel="1">
       <c r="A20" s="5"/>
       <c r="B20" s="11" t="s">
         <v>40</v>
@@ -1535,8 +1846,9 @@
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
-    </row>
-    <row r="21" spans="1:10" outlineLevel="2">
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" outlineLevel="2">
       <c r="A21" s="5"/>
       <c r="B21" s="9"/>
       <c r="C21" s="14" t="s">
@@ -1544,17 +1856,26 @@
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+      <c r="F21" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G21" s="13">
         <v>1000</v>
       </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
+      <c r="H21" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="J21" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K21" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:10" outlineLevel="2">
+    <row r="22" spans="1:11" outlineLevel="2">
       <c r="A22" s="5"/>
       <c r="B22" s="9"/>
       <c r="C22" s="14" t="s">
@@ -1562,17 +1883,26 @@
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="F22" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G22" s="13">
         <v>1000</v>
       </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
+      <c r="H22" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>162</v>
+      </c>
       <c r="J22" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K22" s="13" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:10" outlineLevel="2">
+    <row r="23" spans="1:11" outlineLevel="2">
       <c r="A23" s="5"/>
       <c r="B23" s="9"/>
       <c r="C23" s="14" t="s">
@@ -1580,17 +1910,26 @@
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+      <c r="F23" s="13" t="s">
+        <v>179</v>
+      </c>
       <c r="G23" s="13">
         <v>1000</v>
       </c>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
+      <c r="H23" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>164</v>
+      </c>
       <c r="J23" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K23" s="13" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:10" outlineLevel="2">
+    <row r="24" spans="1:11" outlineLevel="2">
       <c r="A24" s="5"/>
       <c r="B24" s="9"/>
       <c r="C24" s="14" t="s">
@@ -1598,17 +1937,26 @@
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+      <c r="F24" s="13" t="s">
+        <v>179</v>
+      </c>
       <c r="G24" s="13">
         <v>1000</v>
       </c>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
+      <c r="H24" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="J24" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K24" s="13" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:10" outlineLevel="2">
+    <row r="25" spans="1:11" outlineLevel="2">
       <c r="A25" s="5"/>
       <c r="B25" s="9"/>
       <c r="C25" s="14" t="s">
@@ -1616,17 +1964,26 @@
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
+      <c r="F25" s="13" t="s">
+        <v>179</v>
+      </c>
       <c r="G25" s="13">
         <v>1000</v>
       </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
+      <c r="H25" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>198</v>
+      </c>
       <c r="J25" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K25" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:10" outlineLevel="2">
+    <row r="26" spans="1:11" outlineLevel="2">
       <c r="A26" s="5"/>
       <c r="B26" s="10"/>
       <c r="C26" s="14" t="s">
@@ -1634,17 +1991,26 @@
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
+      <c r="F26" s="13" t="s">
+        <v>179</v>
+      </c>
       <c r="G26" s="13">
         <v>1000</v>
       </c>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
+      <c r="H26" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>164</v>
+      </c>
       <c r="J26" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K26" s="13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="27" outlineLevel="1">
+    <row r="27" spans="1:11" ht="27" outlineLevel="1">
       <c r="A27" s="5"/>
       <c r="B27" s="11" t="s">
         <v>89</v>
@@ -1661,8 +2027,9 @@
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
-    </row>
-    <row r="28" spans="1:10" outlineLevel="2">
+      <c r="K27" s="13"/>
+    </row>
+    <row r="28" spans="1:11" outlineLevel="2">
       <c r="A28" s="5"/>
       <c r="B28" s="9"/>
       <c r="C28" s="14" t="s">
@@ -1670,15 +2037,24 @@
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
+      <c r="F28" s="17" t="s">
+        <v>184</v>
+      </c>
       <c r="G28" s="13">
         <v>1000</v>
       </c>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-    </row>
-    <row r="29" spans="1:10" outlineLevel="2">
+      <c r="H28" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K28" s="13"/>
+    </row>
+    <row r="29" spans="1:11" outlineLevel="2">
       <c r="A29" s="5"/>
       <c r="B29" s="9"/>
       <c r="C29" s="14" t="s">
@@ -1686,17 +2062,22 @@
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="13">
         <v>1000</v>
       </c>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="J29" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K29" s="13" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:10" outlineLevel="2">
+    <row r="30" spans="1:11" outlineLevel="2">
       <c r="A30" s="5"/>
       <c r="B30" s="9"/>
       <c r="C30" s="14" t="s">
@@ -1704,17 +2085,22 @@
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
+      <c r="F30" s="19"/>
       <c r="G30" s="13">
         <v>1000</v>
       </c>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="J30" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K30" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="1:10" outlineLevel="2">
+    <row r="31" spans="1:11" outlineLevel="2">
       <c r="A31" s="5"/>
       <c r="B31" s="9"/>
       <c r="C31" s="14" t="s">
@@ -1722,17 +2108,26 @@
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
+      <c r="F31" s="17" t="s">
+        <v>185</v>
+      </c>
       <c r="G31" s="13">
         <v>1000</v>
       </c>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
+      <c r="H31" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>199</v>
+      </c>
       <c r="J31" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K31" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:10" outlineLevel="2">
+    <row r="32" spans="1:11" outlineLevel="2">
       <c r="A32" s="5"/>
       <c r="B32" s="9"/>
       <c r="C32" s="14" t="s">
@@ -1740,17 +2135,22 @@
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
+      <c r="F32" s="18"/>
       <c r="G32" s="13">
         <v>1000</v>
       </c>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="13" t="s">
+        <v>199</v>
+      </c>
       <c r="J32" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K32" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:10" outlineLevel="2">
+    <row r="33" spans="1:11" outlineLevel="2">
       <c r="A33" s="5"/>
       <c r="B33" s="10"/>
       <c r="C33" s="14" t="s">
@@ -1758,17 +2158,22 @@
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
+      <c r="F33" s="19"/>
       <c r="G33" s="13">
         <v>1000</v>
       </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="13" t="s">
+        <v>199</v>
+      </c>
       <c r="J33" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K33" s="13" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:10" outlineLevel="1">
+    <row r="34" spans="1:11" outlineLevel="1">
       <c r="A34" s="5"/>
       <c r="B34" s="11" t="s">
         <v>41</v>
@@ -1781,8 +2186,9 @@
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
-    </row>
-    <row r="35" spans="1:10" outlineLevel="2">
+      <c r="K34" s="13"/>
+    </row>
+    <row r="35" spans="1:11" outlineLevel="2">
       <c r="A35" s="5"/>
       <c r="B35" s="9"/>
       <c r="C35" s="14" t="s">
@@ -1792,15 +2198,24 @@
       <c r="E35" s="13">
         <v>5</v>
       </c>
-      <c r="F35" s="13"/>
+      <c r="F35" s="17" t="s">
+        <v>180</v>
+      </c>
       <c r="G35" s="13">
         <v>2000</v>
       </c>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-    </row>
-    <row r="36" spans="1:10" outlineLevel="2">
+      <c r="H35" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K35" s="13"/>
+    </row>
+    <row r="36" spans="1:11" outlineLevel="2">
       <c r="A36" s="5"/>
       <c r="B36" s="9"/>
       <c r="C36" s="14" t="s">
@@ -1810,15 +2225,20 @@
       <c r="E36" s="13">
         <v>6</v>
       </c>
-      <c r="F36" s="13"/>
+      <c r="F36" s="19"/>
       <c r="G36" s="13">
         <v>2000</v>
       </c>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-    </row>
-    <row r="37" spans="1:10" outlineLevel="2">
+      <c r="H36" s="19"/>
+      <c r="I36" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K36" s="13"/>
+    </row>
+    <row r="37" spans="1:11" outlineLevel="2">
       <c r="A37" s="5"/>
       <c r="B37" s="9"/>
       <c r="C37" s="14" t="s">
@@ -1828,15 +2248,24 @@
       <c r="E37" s="13">
         <v>6</v>
       </c>
-      <c r="F37" s="13"/>
+      <c r="F37" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G37" s="13">
         <v>1500</v>
       </c>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-    </row>
-    <row r="38" spans="1:10" outlineLevel="2">
+      <c r="H37" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K37" s="13"/>
+    </row>
+    <row r="38" spans="1:11" outlineLevel="2">
       <c r="A38" s="5"/>
       <c r="B38" s="9"/>
       <c r="C38" s="14" t="s">
@@ -1846,15 +2275,24 @@
       <c r="E38" s="13">
         <v>6</v>
       </c>
-      <c r="F38" s="13"/>
+      <c r="F38" s="13" t="s">
+        <v>188</v>
+      </c>
       <c r="G38" s="13">
         <v>1500</v>
       </c>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-    </row>
-    <row r="39" spans="1:10" outlineLevel="2">
+      <c r="H38" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K38" s="13"/>
+    </row>
+    <row r="39" spans="1:11" outlineLevel="2">
       <c r="A39" s="5"/>
       <c r="B39" s="9"/>
       <c r="C39" s="14" t="s">
@@ -1864,15 +2302,24 @@
       <c r="E39" s="13">
         <v>6</v>
       </c>
-      <c r="F39" s="13"/>
+      <c r="F39" s="13" t="s">
+        <v>165</v>
+      </c>
       <c r="G39" s="13">
         <v>2000</v>
       </c>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-    </row>
-    <row r="40" spans="1:10" outlineLevel="2">
+      <c r="H39" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K39" s="13"/>
+    </row>
+    <row r="40" spans="1:11" outlineLevel="2">
       <c r="A40" s="5"/>
       <c r="B40" s="9"/>
       <c r="C40" s="14" t="s">
@@ -1882,15 +2329,24 @@
       <c r="E40" s="13">
         <v>4</v>
       </c>
-      <c r="F40" s="13"/>
+      <c r="F40" s="13" t="s">
+        <v>165</v>
+      </c>
       <c r="G40" s="13">
         <v>1500</v>
       </c>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-    </row>
-    <row r="41" spans="1:10" outlineLevel="2">
+      <c r="H40" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K40" s="13"/>
+    </row>
+    <row r="41" spans="1:11" outlineLevel="2">
       <c r="A41" s="5"/>
       <c r="B41" s="10"/>
       <c r="C41" s="14"/>
@@ -1901,8 +2357,9 @@
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
       <c r="J41" s="13"/>
-    </row>
-    <row r="42" spans="1:10" outlineLevel="1">
+      <c r="K41" s="13"/>
+    </row>
+    <row r="42" spans="1:11" outlineLevel="1">
       <c r="A42" s="5"/>
       <c r="B42" s="11" t="s">
         <v>42</v>
@@ -1915,8 +2372,9 @@
       <c r="H42" s="13"/>
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
-    </row>
-    <row r="43" spans="1:10" outlineLevel="2">
+      <c r="K42" s="13"/>
+    </row>
+    <row r="43" spans="1:11" outlineLevel="2">
       <c r="A43" s="5"/>
       <c r="B43" s="9"/>
       <c r="C43" s="14" t="s">
@@ -1926,15 +2384,24 @@
       <c r="E43" s="13">
         <v>8</v>
       </c>
-      <c r="F43" s="13"/>
+      <c r="F43" s="13" t="s">
+        <v>169</v>
+      </c>
       <c r="G43" s="13">
         <v>1000</v>
       </c>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-    </row>
-    <row r="44" spans="1:10" outlineLevel="2">
+      <c r="H43" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K43" s="13"/>
+    </row>
+    <row r="44" spans="1:11" outlineLevel="2">
       <c r="A44" s="5"/>
       <c r="B44" s="9"/>
       <c r="C44" s="14" t="s">
@@ -1944,27 +2411,51 @@
       <c r="E44" s="13">
         <v>8</v>
       </c>
-      <c r="F44" s="13"/>
+      <c r="F44" s="13" t="s">
+        <v>169</v>
+      </c>
       <c r="G44" s="13">
         <v>1000</v>
       </c>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-    </row>
-    <row r="45" spans="1:10" outlineLevel="2">
+      <c r="H44" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K44" s="13"/>
+    </row>
+    <row r="45" spans="1:11" outlineLevel="2">
       <c r="A45" s="5"/>
       <c r="B45" s="9"/>
-      <c r="C45" s="14"/>
+      <c r="C45" s="14" t="s">
+        <v>166</v>
+      </c>
       <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-    </row>
-    <row r="46" spans="1:10" outlineLevel="1">
+      <c r="E45" s="13">
+        <v>8</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="G45" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K45" s="13"/>
+    </row>
+    <row r="46" spans="1:11" outlineLevel="1">
       <c r="A46" s="5"/>
       <c r="B46" s="9"/>
       <c r="C46" s="14"/>
@@ -1975,8 +2466,9 @@
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
-    </row>
-    <row r="47" spans="1:10" outlineLevel="1">
+      <c r="K46" s="13"/>
+    </row>
+    <row r="47" spans="1:11" outlineLevel="1">
       <c r="A47" s="6"/>
       <c r="B47" s="10"/>
       <c r="C47" s="14"/>
@@ -1987,8 +2479,9 @@
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
       <c r="J47" s="13"/>
-    </row>
-    <row r="48" spans="1:10">
+      <c r="K47" s="13"/>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="4" t="s">
         <v>10</v>
       </c>
@@ -2000,8 +2493,9 @@
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
-    </row>
-    <row r="49" spans="1:10" outlineLevel="1">
+      <c r="K48" s="13"/>
+    </row>
+    <row r="49" spans="1:11" outlineLevel="1">
       <c r="A49" s="5"/>
       <c r="B49" s="11" t="s">
         <v>110</v>
@@ -2014,8 +2508,9 @@
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
-    </row>
-    <row r="50" spans="1:10" outlineLevel="2">
+      <c r="K49" s="13"/>
+    </row>
+    <row r="50" spans="1:11" outlineLevel="2">
       <c r="A50" s="5"/>
       <c r="B50" s="9"/>
       <c r="C50" s="14" t="s">
@@ -2025,15 +2520,24 @@
       <c r="E50" s="13">
         <v>5</v>
       </c>
-      <c r="F50" s="13"/>
+      <c r="F50" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G50" s="13">
         <v>5000</v>
       </c>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-    </row>
-    <row r="51" spans="1:10" outlineLevel="2">
+      <c r="H50" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="I50" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K50" s="13"/>
+    </row>
+    <row r="51" spans="1:11" outlineLevel="2">
       <c r="A51" s="5"/>
       <c r="B51" s="9"/>
       <c r="C51" s="14" t="s">
@@ -2043,15 +2547,24 @@
       <c r="E51" s="13">
         <v>5</v>
       </c>
-      <c r="F51" s="13"/>
+      <c r="F51" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G51" s="13">
         <v>3000</v>
       </c>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-    </row>
-    <row r="52" spans="1:10" outlineLevel="2">
+      <c r="H51" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K51" s="13"/>
+    </row>
+    <row r="52" spans="1:11" outlineLevel="2">
       <c r="A52" s="5"/>
       <c r="B52" s="9"/>
       <c r="C52" s="14" t="s">
@@ -2061,15 +2574,24 @@
       <c r="E52" s="13">
         <v>5</v>
       </c>
-      <c r="F52" s="13"/>
+      <c r="F52" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G52" s="13">
         <v>3000</v>
       </c>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
-    </row>
-    <row r="53" spans="1:10" outlineLevel="2">
+      <c r="H52" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J52" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K52" s="13"/>
+    </row>
+    <row r="53" spans="1:11" outlineLevel="2">
       <c r="A53" s="5"/>
       <c r="B53" s="9"/>
       <c r="C53" s="14" t="s">
@@ -2079,13 +2601,24 @@
       <c r="E53" s="13">
         <v>5</v>
       </c>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13"/>
-    </row>
-    <row r="54" spans="1:10" outlineLevel="2">
+      <c r="F53" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G53" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J53" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K53" s="13"/>
+    </row>
+    <row r="54" spans="1:11" outlineLevel="2">
       <c r="A54" s="5"/>
       <c r="B54" s="10"/>
       <c r="C54" s="14" t="s">
@@ -2095,13 +2628,24 @@
       <c r="E54" s="13">
         <v>5</v>
       </c>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-    </row>
-    <row r="55" spans="1:10" outlineLevel="1">
+      <c r="F54" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G54" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="I54" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J54" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K54" s="13"/>
+    </row>
+    <row r="55" spans="1:11" outlineLevel="1">
       <c r="A55" s="5"/>
       <c r="B55" s="11" t="s">
         <v>116</v>
@@ -2114,8 +2658,9 @@
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
-    </row>
-    <row r="56" spans="1:10" outlineLevel="2">
+      <c r="K55" s="13"/>
+    </row>
+    <row r="56" spans="1:11" outlineLevel="2">
       <c r="A56" s="5"/>
       <c r="B56" s="9"/>
       <c r="C56" s="14" t="s">
@@ -2125,15 +2670,24 @@
       <c r="E56" s="13">
         <v>5</v>
       </c>
-      <c r="F56" s="13"/>
+      <c r="F56" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G56" s="13">
         <v>1000</v>
       </c>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-    </row>
-    <row r="57" spans="1:10" outlineLevel="2">
+      <c r="H56" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I56" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="J56" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K56" s="13"/>
+    </row>
+    <row r="57" spans="1:11" outlineLevel="2">
       <c r="A57" s="5"/>
       <c r="B57" s="9"/>
       <c r="C57" s="14" t="s">
@@ -2143,15 +2697,24 @@
       <c r="E57" s="13">
         <v>5</v>
       </c>
-      <c r="F57" s="13"/>
+      <c r="F57" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G57" s="13">
         <v>1000</v>
       </c>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-    </row>
-    <row r="58" spans="1:10" outlineLevel="2">
+      <c r="H57" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="J57" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K57" s="13"/>
+    </row>
+    <row r="58" spans="1:11" outlineLevel="2">
       <c r="A58" s="5"/>
       <c r="B58" s="9"/>
       <c r="C58" s="14" t="s">
@@ -2161,15 +2724,24 @@
       <c r="E58" s="13">
         <v>3</v>
       </c>
-      <c r="F58" s="13"/>
+      <c r="F58" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G58" s="13">
         <v>1000</v>
       </c>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-    </row>
-    <row r="59" spans="1:10" outlineLevel="2">
+      <c r="H58" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I58" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="J58" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K58" s="13"/>
+    </row>
+    <row r="59" spans="1:11" outlineLevel="2">
       <c r="A59" s="5"/>
       <c r="B59" s="10"/>
       <c r="C59" s="14" t="s">
@@ -2179,15 +2751,24 @@
       <c r="E59" s="13">
         <v>1</v>
       </c>
-      <c r="F59" s="13"/>
+      <c r="F59" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G59" s="13">
         <v>1000</v>
       </c>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-    </row>
-    <row r="60" spans="1:10" outlineLevel="1">
+      <c r="H59" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I59" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K59" s="13"/>
+    </row>
+    <row r="60" spans="1:11" outlineLevel="1">
       <c r="A60" s="5"/>
       <c r="B60" s="11" t="s">
         <v>32</v>
@@ -2200,8 +2781,9 @@
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="13"/>
-    </row>
-    <row r="61" spans="1:10" outlineLevel="2">
+      <c r="K60" s="13"/>
+    </row>
+    <row r="61" spans="1:11" outlineLevel="2">
       <c r="A61" s="5"/>
       <c r="B61" s="9"/>
       <c r="C61" s="14" t="s">
@@ -2211,15 +2793,24 @@
       <c r="E61" s="13">
         <v>6</v>
       </c>
-      <c r="F61" s="13"/>
+      <c r="F61" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G61" s="13">
         <v>1000</v>
       </c>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
-    </row>
-    <row r="62" spans="1:10" outlineLevel="2">
+      <c r="H61" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I61" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J61" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K61" s="13"/>
+    </row>
+    <row r="62" spans="1:11" outlineLevel="2">
       <c r="A62" s="5"/>
       <c r="B62" s="9"/>
       <c r="C62" s="14" t="s">
@@ -2229,15 +2820,24 @@
       <c r="E62" s="13">
         <v>5</v>
       </c>
-      <c r="F62" s="13"/>
+      <c r="F62" s="13" t="s">
+        <v>181</v>
+      </c>
       <c r="G62" s="13">
         <v>1000</v>
       </c>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
-    </row>
-    <row r="63" spans="1:10" outlineLevel="2">
+      <c r="H62" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I62" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J62" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K62" s="13"/>
+    </row>
+    <row r="63" spans="1:11" outlineLevel="2">
       <c r="A63" s="5"/>
       <c r="B63" s="9"/>
       <c r="C63" s="14" t="s">
@@ -2247,15 +2847,24 @@
       <c r="E63" s="13">
         <v>6</v>
       </c>
-      <c r="F63" s="13"/>
+      <c r="F63" s="13" t="s">
+        <v>175</v>
+      </c>
       <c r="G63" s="13">
         <v>1000</v>
       </c>
-      <c r="H63" s="13"/>
-      <c r="I63" s="13"/>
-      <c r="J63" s="13"/>
-    </row>
-    <row r="64" spans="1:10" outlineLevel="2">
+      <c r="H63" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I63" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J63" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K63" s="13"/>
+    </row>
+    <row r="64" spans="1:11" outlineLevel="2">
       <c r="A64" s="5"/>
       <c r="B64" s="9"/>
       <c r="C64" s="14" t="s">
@@ -2265,15 +2874,24 @@
       <c r="E64" s="13">
         <v>6</v>
       </c>
-      <c r="F64" s="13"/>
+      <c r="F64" s="13" t="s">
+        <v>182</v>
+      </c>
       <c r="G64" s="13">
         <v>1000</v>
       </c>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13"/>
-    </row>
-    <row r="65" spans="1:10" outlineLevel="2">
+      <c r="H64" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I64" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J64" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K64" s="13"/>
+    </row>
+    <row r="65" spans="1:11" outlineLevel="2">
       <c r="A65" s="5"/>
       <c r="B65" s="9"/>
       <c r="C65" s="14" t="s">
@@ -2283,15 +2901,24 @@
       <c r="E65" s="13">
         <v>5</v>
       </c>
-      <c r="F65" s="13"/>
+      <c r="F65" s="13" t="s">
+        <v>183</v>
+      </c>
       <c r="G65" s="13">
         <v>1000</v>
       </c>
-      <c r="H65" s="13"/>
-      <c r="I65" s="13"/>
-      <c r="J65" s="13"/>
-    </row>
-    <row r="66" spans="1:10" outlineLevel="2">
+      <c r="H65" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I65" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J65" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K65" s="13"/>
+    </row>
+    <row r="66" spans="1:11" outlineLevel="2">
       <c r="A66" s="5"/>
       <c r="B66" s="10"/>
       <c r="C66" s="14"/>
@@ -2302,8 +2929,9 @@
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
       <c r="J66" s="13"/>
-    </row>
-    <row r="67" spans="1:10" outlineLevel="1">
+      <c r="K66" s="13"/>
+    </row>
+    <row r="67" spans="1:11" outlineLevel="1">
       <c r="A67" s="5"/>
       <c r="B67" s="11" t="s">
         <v>33</v>
@@ -2316,8 +2944,9 @@
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
       <c r="J67" s="13"/>
-    </row>
-    <row r="68" spans="1:10" outlineLevel="2">
+      <c r="K67" s="13"/>
+    </row>
+    <row r="68" spans="1:11" outlineLevel="2">
       <c r="A68" s="5"/>
       <c r="B68" s="9"/>
       <c r="C68" s="14" t="s">
@@ -2327,13 +2956,24 @@
       <c r="E68" s="13">
         <v>5</v>
       </c>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-    </row>
-    <row r="69" spans="1:10" outlineLevel="2">
+      <c r="F68" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G68" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="I68" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J68" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K68" s="13"/>
+    </row>
+    <row r="69" spans="1:11" outlineLevel="2">
       <c r="A69" s="5"/>
       <c r="B69" s="9"/>
       <c r="C69" s="14" t="s">
@@ -2343,13 +2983,22 @@
       <c r="E69" s="13">
         <v>5</v>
       </c>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-    </row>
-    <row r="70" spans="1:10" outlineLevel="2">
+      <c r="F69" s="18"/>
+      <c r="G69" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="I69" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J69" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K69" s="13"/>
+    </row>
+    <row r="70" spans="1:11" outlineLevel="2">
       <c r="A70" s="5"/>
       <c r="B70" s="10"/>
       <c r="C70" s="14" t="s">
@@ -2359,13 +3008,22 @@
       <c r="E70" s="13">
         <v>4</v>
       </c>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="13"/>
-    </row>
-    <row r="71" spans="1:10" outlineLevel="1">
+      <c r="F70" s="19"/>
+      <c r="G70" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="I70" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J70" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K70" s="13"/>
+    </row>
+    <row r="71" spans="1:11" outlineLevel="1">
       <c r="A71" s="5"/>
       <c r="B71" s="11" t="s">
         <v>34</v>
@@ -2378,8 +3036,9 @@
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="13"/>
-    </row>
-    <row r="72" spans="1:10" outlineLevel="2">
+      <c r="K71" s="13"/>
+    </row>
+    <row r="72" spans="1:11" outlineLevel="2">
       <c r="A72" s="5"/>
       <c r="B72" s="9"/>
       <c r="C72" s="14" t="s">
@@ -2389,15 +3048,24 @@
       <c r="E72" s="13">
         <v>5</v>
       </c>
-      <c r="F72" s="13"/>
+      <c r="F72" s="17" t="s">
+        <v>170</v>
+      </c>
       <c r="G72" s="13">
         <v>2000</v>
       </c>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-    </row>
-    <row r="73" spans="1:10" outlineLevel="2">
+      <c r="H72" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="I72" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J72" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K72" s="13"/>
+    </row>
+    <row r="73" spans="1:11" outlineLevel="2">
       <c r="A73" s="5"/>
       <c r="B73" s="9"/>
       <c r="C73" s="14" t="s">
@@ -2407,15 +3075,20 @@
       <c r="E73" s="13">
         <v>4</v>
       </c>
-      <c r="F73" s="13"/>
+      <c r="F73" s="18"/>
       <c r="G73" s="13">
         <v>1000</v>
       </c>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
-    </row>
-    <row r="74" spans="1:10" outlineLevel="2">
+      <c r="H73" s="18"/>
+      <c r="I73" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J73" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K73" s="13"/>
+    </row>
+    <row r="74" spans="1:11" outlineLevel="2">
       <c r="A74" s="5"/>
       <c r="B74" s="9"/>
       <c r="C74" s="14" t="s">
@@ -2425,15 +3098,20 @@
       <c r="E74" s="13">
         <v>5</v>
       </c>
-      <c r="F74" s="13"/>
+      <c r="F74" s="18"/>
       <c r="G74" s="13">
         <v>2000</v>
       </c>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-    </row>
-    <row r="75" spans="1:10" outlineLevel="2">
+      <c r="H74" s="18"/>
+      <c r="I74" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J74" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K74" s="13"/>
+    </row>
+    <row r="75" spans="1:11" outlineLevel="2">
       <c r="A75" s="5"/>
       <c r="B75" s="9"/>
       <c r="C75" s="14" t="s">
@@ -2443,69 +3121,103 @@
       <c r="E75" s="13">
         <v>5</v>
       </c>
-      <c r="F75" s="13"/>
+      <c r="F75" s="19"/>
       <c r="G75" s="13">
         <v>3000</v>
       </c>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
-      <c r="J75" s="13"/>
-    </row>
-    <row r="76" spans="1:10" outlineLevel="2">
+      <c r="H75" s="19"/>
+      <c r="I75" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J75" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K75" s="13"/>
+    </row>
+    <row r="76" spans="1:11" ht="27" outlineLevel="2">
       <c r="A76" s="5"/>
       <c r="B76" s="9"/>
       <c r="C76" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D76" s="13"/>
+      <c r="D76" s="14" t="s">
+        <v>193</v>
+      </c>
       <c r="E76" s="13">
         <v>3</v>
       </c>
-      <c r="F76" s="13"/>
+      <c r="F76" s="13" t="s">
+        <v>191</v>
+      </c>
       <c r="G76" s="13">
         <v>1000</v>
       </c>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
-      <c r="J76" s="13"/>
-    </row>
-    <row r="77" spans="1:10" outlineLevel="2">
+      <c r="H76" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K76" s="13"/>
+    </row>
+    <row r="77" spans="1:11" outlineLevel="2">
       <c r="A77" s="5"/>
       <c r="B77" s="9"/>
       <c r="C77" s="14" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
       <c r="D77" s="13"/>
       <c r="E77" s="13">
         <v>3</v>
       </c>
-      <c r="F77" s="13"/>
+      <c r="F77" s="13" t="s">
+        <v>191</v>
+      </c>
       <c r="G77" s="13">
         <v>1000</v>
       </c>
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
-      <c r="J77" s="13"/>
-    </row>
-    <row r="78" spans="1:10" outlineLevel="2">
+      <c r="H77" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="J77" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K77" s="13"/>
+    </row>
+    <row r="78" spans="1:11" outlineLevel="2">
       <c r="A78" s="5"/>
       <c r="B78" s="10"/>
       <c r="C78" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D78" s="13"/>
       <c r="E78" s="13">
         <v>5</v>
       </c>
-      <c r="F78" s="13"/>
+      <c r="F78" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G78" s="13">
         <v>3000</v>
       </c>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-      <c r="J78" s="13"/>
-    </row>
-    <row r="79" spans="1:10" outlineLevel="1">
+      <c r="H78" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="I78" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="J78" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K78" s="13"/>
+    </row>
+    <row r="79" spans="1:11" outlineLevel="1">
       <c r="A79" s="5"/>
       <c r="B79" s="11" t="s">
         <v>35</v>
@@ -2518,116 +3230,171 @@
       <c r="H79" s="13"/>
       <c r="I79" s="13"/>
       <c r="J79" s="13"/>
-    </row>
-    <row r="80" spans="1:10" outlineLevel="2">
+      <c r="K79" s="13"/>
+    </row>
+    <row r="80" spans="1:11" outlineLevel="2">
       <c r="A80" s="5"/>
       <c r="B80" s="9"/>
       <c r="C80" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D80" s="13"/>
       <c r="E80" s="13">
         <v>5</v>
       </c>
-      <c r="F80" s="13"/>
+      <c r="F80" s="13" t="s">
+        <v>191</v>
+      </c>
       <c r="G80" s="13">
         <v>2000</v>
       </c>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
-      <c r="J80" s="13"/>
-    </row>
-    <row r="81" spans="1:10" outlineLevel="2">
+      <c r="H80" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="I80" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="J80" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K80" s="13"/>
+    </row>
+    <row r="81" spans="1:11" outlineLevel="2">
       <c r="A81" s="5"/>
       <c r="B81" s="9"/>
       <c r="C81" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D81" s="13"/>
       <c r="E81" s="13">
         <v>5</v>
       </c>
-      <c r="F81" s="13"/>
+      <c r="F81" s="13" t="s">
+        <v>191</v>
+      </c>
       <c r="G81" s="13">
         <v>1500</v>
       </c>
-      <c r="H81" s="13"/>
-      <c r="I81" s="13"/>
-      <c r="J81" s="13"/>
-    </row>
-    <row r="82" spans="1:10" outlineLevel="2">
+      <c r="H81" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="I81" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="J81" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K81" s="13"/>
+    </row>
+    <row r="82" spans="1:11" outlineLevel="2">
       <c r="A82" s="5"/>
       <c r="B82" s="9"/>
       <c r="C82" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D82" s="13"/>
       <c r="E82" s="13">
         <v>3</v>
       </c>
-      <c r="F82" s="13"/>
+      <c r="F82" s="13" t="s">
+        <v>191</v>
+      </c>
       <c r="G82" s="13">
         <v>3000</v>
       </c>
-      <c r="H82" s="13"/>
-      <c r="I82" s="13"/>
-      <c r="J82" s="13"/>
-    </row>
-    <row r="83" spans="1:10" outlineLevel="2">
+      <c r="H82" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="I82" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="J82" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K82" s="13"/>
+    </row>
+    <row r="83" spans="1:11" outlineLevel="2">
       <c r="A83" s="5"/>
       <c r="B83" s="9"/>
       <c r="C83" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D83" s="13"/>
       <c r="E83" s="13">
         <v>6</v>
       </c>
-      <c r="F83" s="13"/>
+      <c r="F83" s="13" t="s">
+        <v>184</v>
+      </c>
       <c r="G83" s="13">
         <v>5000</v>
       </c>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="13"/>
-    </row>
-    <row r="84" spans="1:10" outlineLevel="2">
+      <c r="H83" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="J83" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K83" s="13"/>
+    </row>
+    <row r="84" spans="1:11" outlineLevel="2">
       <c r="A84" s="5"/>
       <c r="B84" s="9"/>
       <c r="C84" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D84" s="13"/>
       <c r="E84" s="13">
         <v>6</v>
       </c>
-      <c r="F84" s="13"/>
+      <c r="F84" s="13" t="s">
+        <v>191</v>
+      </c>
       <c r="G84" s="13">
         <v>3000</v>
       </c>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="13"/>
-    </row>
-    <row r="85" spans="1:10" outlineLevel="2">
+      <c r="H84" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I84" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="J84" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K84" s="13"/>
+    </row>
+    <row r="85" spans="1:11" outlineLevel="2">
       <c r="A85" s="5"/>
       <c r="B85" s="10"/>
       <c r="C85" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D85" s="13"/>
       <c r="E85" s="13">
         <v>4</v>
       </c>
-      <c r="F85" s="13"/>
+      <c r="F85" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G85" s="13">
         <v>1000</v>
       </c>
-      <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
-      <c r="J85" s="13"/>
-    </row>
-    <row r="86" spans="1:10" ht="11.25" customHeight="1" outlineLevel="1">
+      <c r="H85" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I85" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J85" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K85" s="13"/>
+    </row>
+    <row r="86" spans="1:11" ht="11.25" customHeight="1" outlineLevel="1">
       <c r="A86" s="5"/>
       <c r="B86" s="11" t="s">
         <v>36</v>
@@ -2640,80 +3407,117 @@
       <c r="H86" s="13"/>
       <c r="I86" s="13"/>
       <c r="J86" s="13"/>
-    </row>
-    <row r="87" spans="1:10" outlineLevel="2">
+      <c r="K86" s="13"/>
+    </row>
+    <row r="87" spans="1:11" outlineLevel="2">
       <c r="A87" s="5"/>
       <c r="B87" s="9"/>
       <c r="C87" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D87" s="13"/>
       <c r="E87" s="13">
         <v>5</v>
       </c>
-      <c r="F87" s="13"/>
+      <c r="F87" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G87" s="13">
         <v>2000</v>
       </c>
-      <c r="H87" s="13"/>
-      <c r="I87" s="13"/>
-      <c r="J87" s="13"/>
-    </row>
-    <row r="88" spans="1:10" outlineLevel="2">
+      <c r="H87" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I87" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J87" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K87" s="13"/>
+    </row>
+    <row r="88" spans="1:11" outlineLevel="2">
       <c r="A88" s="5"/>
       <c r="B88" s="9"/>
       <c r="C88" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D88" s="13"/>
       <c r="E88" s="13">
         <v>5</v>
       </c>
-      <c r="F88" s="13"/>
+      <c r="F88" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G88" s="13">
         <v>2000</v>
       </c>
-      <c r="H88" s="13"/>
-      <c r="I88" s="13"/>
-      <c r="J88" s="13"/>
-    </row>
-    <row r="89" spans="1:10" outlineLevel="2">
+      <c r="H88" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I88" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J88" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K88" s="13"/>
+    </row>
+    <row r="89" spans="1:11" outlineLevel="2">
       <c r="A89" s="5"/>
       <c r="B89" s="9"/>
       <c r="C89" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D89" s="13"/>
       <c r="E89" s="13">
         <v>5</v>
       </c>
-      <c r="F89" s="13"/>
+      <c r="F89" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G89" s="13">
         <v>1000</v>
       </c>
-      <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
-      <c r="J89" s="13"/>
-    </row>
-    <row r="90" spans="1:10" outlineLevel="2">
+      <c r="H89" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I89" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="J89" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K89" s="13"/>
+    </row>
+    <row r="90" spans="1:11" outlineLevel="2">
       <c r="A90" s="5"/>
       <c r="B90" s="10"/>
       <c r="C90" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D90" s="13"/>
       <c r="E90" s="13">
         <v>5</v>
       </c>
-      <c r="F90" s="13"/>
+      <c r="F90" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G90" s="13">
         <v>2000</v>
       </c>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
-      <c r="J90" s="13"/>
-    </row>
-    <row r="91" spans="1:10" outlineLevel="1">
+      <c r="H90" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="J90" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K90" s="13"/>
+    </row>
+    <row r="91" spans="1:11" outlineLevel="1">
       <c r="A91" s="5"/>
       <c r="B91" s="11" t="s">
         <v>104</v>
@@ -2726,80 +3530,117 @@
       <c r="H91" s="13"/>
       <c r="I91" s="13"/>
       <c r="J91" s="13"/>
-    </row>
-    <row r="92" spans="1:10" outlineLevel="2">
+      <c r="K91" s="13"/>
+    </row>
+    <row r="92" spans="1:11" outlineLevel="2">
       <c r="A92" s="5"/>
       <c r="B92" s="9"/>
       <c r="C92" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D92" s="13"/>
       <c r="E92" s="13">
         <v>5</v>
       </c>
-      <c r="F92" s="13"/>
+      <c r="F92" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G92" s="13">
         <v>1000</v>
       </c>
-      <c r="H92" s="13"/>
-      <c r="I92" s="13"/>
-      <c r="J92" s="13"/>
-    </row>
-    <row r="93" spans="1:10" outlineLevel="2">
+      <c r="H92" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I92" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J92" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K92" s="13"/>
+    </row>
+    <row r="93" spans="1:11" outlineLevel="2">
       <c r="A93" s="5"/>
       <c r="B93" s="9"/>
       <c r="C93" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D93" s="13"/>
       <c r="E93" s="13">
         <v>5</v>
       </c>
-      <c r="F93" s="13"/>
+      <c r="F93" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G93" s="13">
         <v>1000</v>
       </c>
-      <c r="H93" s="13"/>
-      <c r="I93" s="13"/>
-      <c r="J93" s="13"/>
-    </row>
-    <row r="94" spans="1:10" outlineLevel="2">
+      <c r="H93" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I93" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J93" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K93" s="13"/>
+    </row>
+    <row r="94" spans="1:11" outlineLevel="2">
       <c r="A94" s="5"/>
       <c r="B94" s="9"/>
       <c r="C94" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D94" s="13"/>
       <c r="E94" s="13">
         <v>5</v>
       </c>
-      <c r="F94" s="13"/>
+      <c r="F94" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G94" s="13">
         <v>1000</v>
       </c>
-      <c r="H94" s="13"/>
-      <c r="I94" s="13"/>
-      <c r="J94" s="13"/>
-    </row>
-    <row r="95" spans="1:10" outlineLevel="2">
+      <c r="H94" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I94" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J94" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K94" s="13"/>
+    </row>
+    <row r="95" spans="1:11" outlineLevel="2">
       <c r="A95" s="5"/>
       <c r="B95" s="10"/>
       <c r="C95" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D95" s="13"/>
       <c r="E95" s="13">
         <v>5</v>
       </c>
-      <c r="F95" s="13"/>
+      <c r="F95" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G95" s="13">
         <v>1000</v>
       </c>
-      <c r="H95" s="13"/>
-      <c r="I95" s="13"/>
-      <c r="J95" s="13"/>
-    </row>
-    <row r="96" spans="1:10" outlineLevel="1">
+      <c r="H95" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="I95" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="J95" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K95" s="13"/>
+    </row>
+    <row r="96" spans="1:11" outlineLevel="1">
       <c r="A96" s="5"/>
       <c r="B96" s="11" t="s">
         <v>124</v>
@@ -2812,47 +3653,66 @@
       <c r="H96" s="13"/>
       <c r="I96" s="13"/>
       <c r="J96" s="13"/>
-    </row>
-    <row r="97" spans="1:10" outlineLevel="2">
+      <c r="K96" s="13"/>
+    </row>
+    <row r="97" spans="1:11" outlineLevel="2">
       <c r="A97" s="5"/>
       <c r="B97" s="9"/>
       <c r="C97" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D97" s="13"/>
       <c r="E97" s="13">
         <v>4</v>
       </c>
-      <c r="F97" s="13"/>
+      <c r="F97" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G97" s="13">
         <v>1000</v>
       </c>
-      <c r="H97" s="13"/>
-      <c r="I97" s="13"/>
-      <c r="J97" s="13"/>
-    </row>
-    <row r="98" spans="1:10" outlineLevel="2">
+      <c r="H97" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I97" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J97" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K97" s="13"/>
+    </row>
+    <row r="98" spans="1:11" outlineLevel="2">
       <c r="A98" s="5"/>
       <c r="B98" s="10"/>
       <c r="C98" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D98" s="13"/>
       <c r="E98" s="13">
         <v>4</v>
       </c>
-      <c r="F98" s="13"/>
+      <c r="F98" s="13" t="s">
+        <v>180</v>
+      </c>
       <c r="G98" s="13">
-        <v>2000</v>
-      </c>
-      <c r="H98" s="13"/>
-      <c r="I98" s="13"/>
-      <c r="J98" s="13"/>
-    </row>
-    <row r="99" spans="1:10" outlineLevel="1">
+        <v>1000</v>
+      </c>
+      <c r="H98" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="I98" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="J98" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K98" s="13"/>
+    </row>
+    <row r="99" spans="1:11" outlineLevel="1">
       <c r="A99" s="5"/>
       <c r="B99" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C99" s="14"/>
       <c r="D99" s="13"/>
@@ -2862,67 +3722,87 @@
       <c r="H99" s="13"/>
       <c r="I99" s="13"/>
       <c r="J99" s="13"/>
-    </row>
-    <row r="100" spans="1:10" outlineLevel="2">
+      <c r="K99" s="13"/>
+    </row>
+    <row r="100" spans="1:11" outlineLevel="2">
       <c r="A100" s="5"/>
       <c r="B100" s="9"/>
       <c r="C100" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D100" s="13"/>
       <c r="E100" s="13">
         <v>4</v>
       </c>
-      <c r="F100" s="13"/>
+      <c r="F100" s="17" t="s">
+        <v>180</v>
+      </c>
       <c r="G100" s="13">
         <v>1000</v>
       </c>
-      <c r="H100" s="13"/>
-      <c r="I100" s="13"/>
-      <c r="J100" s="13"/>
-    </row>
-    <row r="101" spans="1:10" outlineLevel="2">
+      <c r="H100" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="I100" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J100" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K100" s="13"/>
+    </row>
+    <row r="101" spans="1:11" outlineLevel="2">
       <c r="A101" s="5"/>
       <c r="B101" s="9"/>
       <c r="C101" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D101" s="13"/>
       <c r="E101" s="13">
         <v>4</v>
       </c>
-      <c r="F101" s="13"/>
+      <c r="F101" s="18"/>
       <c r="G101" s="13">
         <v>1000</v>
       </c>
-      <c r="H101" s="13"/>
-      <c r="I101" s="13"/>
-      <c r="J101" s="13"/>
-    </row>
-    <row r="102" spans="1:10" outlineLevel="2">
+      <c r="H101" s="18"/>
+      <c r="I101" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J101" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K101" s="13"/>
+    </row>
+    <row r="102" spans="1:11" outlineLevel="2">
       <c r="A102" s="6"/>
       <c r="B102" s="10"/>
       <c r="C102" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D102" s="13"/>
       <c r="E102" s="13">
         <v>4</v>
       </c>
-      <c r="F102" s="13"/>
+      <c r="F102" s="19"/>
       <c r="G102" s="13">
         <v>5000</v>
       </c>
-      <c r="H102" s="13"/>
-      <c r="I102" s="13"/>
-      <c r="J102" s="13"/>
-    </row>
-    <row r="103" spans="1:10">
+      <c r="H102" s="19"/>
+      <c r="I102" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J102" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K102" s="13"/>
+    </row>
+    <row r="103" spans="1:11">
       <c r="A103" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C103" s="14"/>
       <c r="D103" s="13"/>
@@ -2932,8 +3812,9 @@
       <c r="H103" s="13"/>
       <c r="I103" s="13"/>
       <c r="J103" s="13"/>
-    </row>
-    <row r="104" spans="1:10" outlineLevel="1">
+      <c r="K103" s="13"/>
+    </row>
+    <row r="104" spans="1:11" outlineLevel="1">
       <c r="A104" s="5"/>
       <c r="B104" s="11" t="s">
         <v>47</v>
@@ -2943,15 +3824,24 @@
       <c r="E104" s="13">
         <v>7</v>
       </c>
-      <c r="F104" s="13"/>
+      <c r="F104" s="13" t="s">
+        <v>173</v>
+      </c>
       <c r="G104" s="13">
         <v>5000</v>
       </c>
-      <c r="H104" s="13"/>
-      <c r="I104" s="13"/>
-      <c r="J104" s="13"/>
-    </row>
-    <row r="105" spans="1:10" outlineLevel="1">
+      <c r="H104" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="I104" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J104" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K104" s="13"/>
+    </row>
+    <row r="105" spans="1:11" outlineLevel="1">
       <c r="A105" s="5"/>
       <c r="B105" s="9" t="s">
         <v>46</v>
@@ -2961,15 +3851,24 @@
       <c r="E105" s="13">
         <v>7</v>
       </c>
-      <c r="F105" s="13"/>
+      <c r="F105" s="13" t="s">
+        <v>173</v>
+      </c>
       <c r="G105" s="13">
         <v>5000</v>
       </c>
-      <c r="H105" s="13"/>
-      <c r="I105" s="13"/>
-      <c r="J105" s="13"/>
-    </row>
-    <row r="106" spans="1:10" outlineLevel="1">
+      <c r="H105" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="I105" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="J105" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K105" s="13"/>
+    </row>
+    <row r="106" spans="1:11" outlineLevel="1">
       <c r="A106" s="5"/>
       <c r="B106" s="9" t="s">
         <v>45</v>
@@ -2979,15 +3878,24 @@
       <c r="E106" s="13">
         <v>7</v>
       </c>
-      <c r="F106" s="13"/>
+      <c r="F106" s="13" t="s">
+        <v>173</v>
+      </c>
       <c r="G106" s="13">
         <v>5000</v>
       </c>
-      <c r="H106" s="13"/>
-      <c r="I106" s="13"/>
-      <c r="J106" s="13"/>
-    </row>
-    <row r="107" spans="1:10" outlineLevel="1">
+      <c r="H106" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="I106" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J106" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K106" s="13"/>
+    </row>
+    <row r="107" spans="1:11" outlineLevel="1">
       <c r="A107" s="5"/>
       <c r="B107" s="9" t="s">
         <v>44</v>
@@ -2997,15 +3905,24 @@
       <c r="E107" s="13">
         <v>7</v>
       </c>
-      <c r="F107" s="13"/>
+      <c r="F107" s="13" t="s">
+        <v>173</v>
+      </c>
       <c r="G107" s="13">
         <v>5000</v>
       </c>
-      <c r="H107" s="13"/>
-      <c r="I107" s="13"/>
-      <c r="J107" s="13"/>
-    </row>
-    <row r="108" spans="1:10" outlineLevel="1">
+      <c r="H107" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="I107" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J107" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K107" s="13"/>
+    </row>
+    <row r="108" spans="1:11" outlineLevel="1">
       <c r="A108" s="6"/>
       <c r="B108" s="10"/>
       <c r="C108" s="14"/>
@@ -3016,8 +3933,9 @@
       <c r="H108" s="13"/>
       <c r="I108" s="13"/>
       <c r="J108" s="13"/>
-    </row>
-    <row r="109" spans="1:10">
+      <c r="K108" s="13"/>
+    </row>
+    <row r="109" spans="1:11">
       <c r="A109" s="4" t="s">
         <v>12</v>
       </c>
@@ -3029,11 +3947,12 @@
       <c r="H109" s="13"/>
       <c r="I109" s="13"/>
       <c r="J109" s="13"/>
-    </row>
-    <row r="110" spans="1:10" outlineLevel="1">
+      <c r="K109" s="13"/>
+    </row>
+    <row r="110" spans="1:11" outlineLevel="1">
       <c r="A110" s="5"/>
       <c r="B110" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C110" s="14"/>
       <c r="D110" s="13"/>
@@ -3043,8 +3962,9 @@
       <c r="H110" s="13"/>
       <c r="I110" s="13"/>
       <c r="J110" s="13"/>
-    </row>
-    <row r="111" spans="1:10" outlineLevel="1">
+      <c r="K110" s="13"/>
+    </row>
+    <row r="111" spans="1:11" outlineLevel="1">
       <c r="A111" s="5"/>
       <c r="B111" s="9"/>
       <c r="C111" s="14"/>
@@ -3055,8 +3975,9 @@
       <c r="H111" s="13"/>
       <c r="I111" s="13"/>
       <c r="J111" s="13"/>
-    </row>
-    <row r="112" spans="1:10" outlineLevel="1">
+      <c r="K111" s="13"/>
+    </row>
+    <row r="112" spans="1:11" outlineLevel="1">
       <c r="A112" s="5"/>
       <c r="B112" s="9"/>
       <c r="C112" s="14"/>
@@ -3067,8 +3988,9 @@
       <c r="H112" s="13"/>
       <c r="I112" s="13"/>
       <c r="J112" s="13"/>
-    </row>
-    <row r="113" spans="1:10" outlineLevel="1">
+      <c r="K112" s="13"/>
+    </row>
+    <row r="113" spans="1:11" outlineLevel="1">
       <c r="A113" s="6"/>
       <c r="B113" s="10"/>
       <c r="C113" s="14"/>
@@ -3079,8 +4001,9 @@
       <c r="H113" s="13"/>
       <c r="I113" s="13"/>
       <c r="J113" s="13"/>
-    </row>
-    <row r="114" spans="1:10">
+      <c r="K113" s="13"/>
+    </row>
+    <row r="114" spans="1:11">
       <c r="A114" s="4" t="s">
         <v>13</v>
       </c>
@@ -3092,8 +4015,9 @@
       <c r="H114" s="13"/>
       <c r="I114" s="13"/>
       <c r="J114" s="13"/>
-    </row>
-    <row r="115" spans="1:10" outlineLevel="1">
+      <c r="K114" s="13"/>
+    </row>
+    <row r="115" spans="1:11" outlineLevel="1">
       <c r="A115" s="5"/>
       <c r="B115" s="11" t="s">
         <v>43</v>
@@ -3106,12 +4030,13 @@
       <c r="H115" s="13"/>
       <c r="I115" s="13"/>
       <c r="J115" s="13"/>
-    </row>
-    <row r="116" spans="1:10" outlineLevel="1">
+      <c r="K115" s="13"/>
+    </row>
+    <row r="116" spans="1:11" outlineLevel="1">
       <c r="A116" s="5"/>
       <c r="B116" s="9"/>
       <c r="C116" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D116" s="13"/>
       <c r="E116" s="13"/>
@@ -3119,13 +4044,16 @@
       <c r="G116" s="13"/>
       <c r="H116" s="13"/>
       <c r="I116" s="13"/>
-      <c r="J116" s="13"/>
-    </row>
-    <row r="117" spans="1:10" outlineLevel="1">
+      <c r="J116" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K116" s="13"/>
+    </row>
+    <row r="117" spans="1:11" outlineLevel="1">
       <c r="A117" s="5"/>
       <c r="B117" s="9"/>
       <c r="C117" s="16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D117" s="13"/>
       <c r="E117" s="13"/>
@@ -3133,13 +4061,16 @@
       <c r="G117" s="13"/>
       <c r="H117" s="13"/>
       <c r="I117" s="13"/>
-      <c r="J117" s="13"/>
-    </row>
-    <row r="118" spans="1:10" outlineLevel="1">
+      <c r="J117" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K117" s="13"/>
+    </row>
+    <row r="118" spans="1:11" outlineLevel="1">
       <c r="A118" s="5"/>
       <c r="B118" s="9"/>
       <c r="C118" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D118" s="13"/>
       <c r="E118" s="13"/>
@@ -3147,13 +4078,16 @@
       <c r="G118" s="13"/>
       <c r="H118" s="13"/>
       <c r="I118" s="13"/>
-      <c r="J118" s="13"/>
-    </row>
-    <row r="119" spans="1:10" outlineLevel="1">
+      <c r="J118" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K118" s="13"/>
+    </row>
+    <row r="119" spans="1:11" outlineLevel="1">
       <c r="A119" s="5"/>
       <c r="B119" s="9"/>
       <c r="C119" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D119" s="13"/>
       <c r="E119" s="13"/>
@@ -3161,13 +4095,16 @@
       <c r="G119" s="13"/>
       <c r="H119" s="13"/>
       <c r="I119" s="13"/>
-      <c r="J119" s="13"/>
-    </row>
-    <row r="120" spans="1:10" outlineLevel="1">
+      <c r="J119" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K119" s="13"/>
+    </row>
+    <row r="120" spans="1:11" outlineLevel="1">
       <c r="A120" s="6"/>
       <c r="B120" s="10"/>
       <c r="C120" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D120" s="13"/>
       <c r="E120" s="13"/>
@@ -3175,9 +4112,18 @@
       <c r="G120" s="13"/>
       <c r="H120" s="13"/>
       <c r="I120" s="13"/>
-      <c r="J120" s="13"/>
-    </row>
-    <row r="121" spans="1:10">
+      <c r="J120" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K120" s="13"/>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>158</v>
+      </c>
       <c r="C121" s="14"/>
       <c r="D121" s="13"/>
       <c r="E121" s="13"/>
@@ -3186,8 +4132,12 @@
       <c r="H121" s="13"/>
       <c r="I121" s="13"/>
       <c r="J121" s="13"/>
-    </row>
-    <row r="122" spans="1:10">
+      <c r="K121" s="13"/>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="B122" s="7" t="s">
+        <v>159</v>
+      </c>
       <c r="C122" s="14"/>
       <c r="D122" s="13"/>
       <c r="E122" s="13"/>
@@ -3196,9 +4146,28 @@
       <c r="H122" s="13"/>
       <c r="I122" s="13"/>
       <c r="J122" s="13"/>
+      <c r="K122" s="13"/>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="B123" s="7" t="s">
+        <v>160</v>
+      </c>
     </row>
   </sheetData>
   <dataConsolidate/>
+  <mergeCells count="11">
+    <mergeCell ref="F68:F70"/>
+    <mergeCell ref="F72:F75"/>
+    <mergeCell ref="H72:H75"/>
+    <mergeCell ref="F100:F102"/>
+    <mergeCell ref="H100:H102"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="H35:H36"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/internal_doc/00.项目管理/00.任务计划/对外文档规划表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/对外文档规划表.xlsx
@@ -11,6 +11,9 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$40</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -853,7 +856,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -875,6 +878,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -989,7 +1022,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1015,6 +1048,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
@@ -1049,6 +1085,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1365,7 +1416,7 @@
       <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -1406,2396 +1457,2396 @@
     </row>
     <row r="4" spans="1:11" ht="67.5" outlineLevel="2">
       <c r="A4" s="5"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="14" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="14">
         <v>8</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="14">
         <v>10000</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="67.5" outlineLevel="2">
       <c r="A5" s="5"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="14" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="14">
         <v>4</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="14">
         <v>5000</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K5" s="13"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" spans="1:11" ht="54" outlineLevel="2">
       <c r="A6" s="5"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <v>7</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <v>8000</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="14" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="67.5" outlineLevel="2">
       <c r="A7" s="5"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="14" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="14">
         <v>7</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="14">
         <v>5000</v>
       </c>
-      <c r="H7" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="I7" s="13" t="s">
+      <c r="H7" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="67.5" outlineLevel="2">
       <c r="A8" s="5"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="14">
         <v>7</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <v>20000</v>
       </c>
-      <c r="H8" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="I8" s="13" t="s">
+      <c r="H8" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="I8" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="54" outlineLevel="2">
       <c r="A9" s="5"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="14" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <v>5</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <v>5000</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="40.5" outlineLevel="2">
       <c r="A10" s="5"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="14" t="s">
+      <c r="B10" s="11"/>
+      <c r="C10" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="14">
         <v>6</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="14">
         <v>8000</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="14" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:11" outlineLevel="1">
       <c r="A11" s="5"/>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
     </row>
     <row r="12" spans="1:11" ht="40.5" outlineLevel="2">
       <c r="A12" s="5"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="10"/>
+      <c r="C12" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="14">
         <v>8</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <v>1500</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K12" s="13"/>
+      <c r="K12" s="14"/>
     </row>
     <row r="13" spans="1:11" ht="27" outlineLevel="2">
       <c r="A13" s="5"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="14" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="14">
         <v>8</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <v>20000</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K13" s="13"/>
+      <c r="K13" s="14"/>
     </row>
     <row r="14" spans="1:11" ht="40.5" outlineLevel="2">
       <c r="A14" s="5"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="14" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="14">
         <v>8</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="14">
         <v>20000</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H14" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K14" s="13"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" spans="1:11" outlineLevel="2">
       <c r="A15" s="5"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="14" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="14">
         <v>8</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="14">
         <v>5000</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="H15" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="I15" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K15" s="13"/>
+      <c r="K15" s="14"/>
     </row>
     <row r="16" spans="1:11" ht="40.5" outlineLevel="2">
       <c r="A16" s="5"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="14" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="14">
         <v>8</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="14">
         <v>5000</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="H16" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K16" s="13"/>
+      <c r="K16" s="14"/>
     </row>
     <row r="17" spans="1:11" outlineLevel="1">
       <c r="A17" s="5"/>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
     </row>
     <row r="18" spans="1:11" outlineLevel="1">
       <c r="A18" s="6"/>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
     </row>
     <row r="20" spans="1:11" ht="40.5" outlineLevel="1">
       <c r="A20" s="5"/>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="14">
         <v>7</v>
       </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
     </row>
     <row r="21" spans="1:11" outlineLevel="2">
       <c r="A21" s="5"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="14" t="s">
+      <c r="B21" s="10"/>
+      <c r="C21" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13" t="s">
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="14">
         <v>1000</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I21" s="13" t="s">
+      <c r="I21" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J21" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K21" s="13" t="s">
+      <c r="J21" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K21" s="14" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:11" outlineLevel="2">
       <c r="A22" s="5"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="14" t="s">
+      <c r="B22" s="10"/>
+      <c r="C22" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13" t="s">
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="14">
         <v>1000</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I22" s="13" t="s">
+      <c r="I22" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J22" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K22" s="13" t="s">
+      <c r="J22" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K22" s="14" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:11" outlineLevel="2">
       <c r="A23" s="5"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="14" t="s">
+      <c r="B23" s="10"/>
+      <c r="C23" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13" t="s">
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="14">
         <v>1000</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="H23" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="I23" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="J23" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K23" s="13" t="s">
+      <c r="J23" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K23" s="14" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:11" outlineLevel="2">
       <c r="A24" s="5"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="14" t="s">
+      <c r="B24" s="10"/>
+      <c r="C24" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13" t="s">
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="14">
         <v>1000</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H24" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="I24" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J24" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K24" s="13" t="s">
+      <c r="J24" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K24" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:11" outlineLevel="2">
       <c r="A25" s="5"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="14" t="s">
+      <c r="B25" s="10"/>
+      <c r="C25" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13" t="s">
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="14">
         <v>1000</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H25" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I25" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J25" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K25" s="13" t="s">
+      <c r="J25" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K25" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:11" outlineLevel="2">
       <c r="A26" s="5"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="14" t="s">
+      <c r="B26" s="11"/>
+      <c r="C26" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13" t="s">
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="14">
         <v>1000</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="H26" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="I26" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="J26" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K26" s="13" t="s">
+      <c r="J26" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K26" s="14" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="27" outlineLevel="1">
       <c r="A27" s="5"/>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13">
+      <c r="D27" s="14"/>
+      <c r="E27" s="14">
         <v>7</v>
       </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
     </row>
     <row r="28" spans="1:11" outlineLevel="2">
       <c r="A28" s="5"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="14" t="s">
+      <c r="B28" s="10"/>
+      <c r="C28" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="17" t="s">
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="14">
         <v>1000</v>
       </c>
-      <c r="H28" s="17" t="s">
+      <c r="H28" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="I28" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J28" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K28" s="13"/>
+      <c r="J28" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K28" s="14"/>
     </row>
     <row r="29" spans="1:11" outlineLevel="2">
       <c r="A29" s="5"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="14" t="s">
+      <c r="B29" s="10"/>
+      <c r="C29" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="13">
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="14">
         <v>1000</v>
       </c>
-      <c r="H29" s="18"/>
-      <c r="I29" s="13" t="s">
+      <c r="H29" s="19"/>
+      <c r="I29" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K29" s="13" t="s">
+      <c r="J29" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K29" s="14" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:11" outlineLevel="2">
       <c r="A30" s="5"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="14" t="s">
+      <c r="B30" s="10"/>
+      <c r="C30" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="13">
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="14">
         <v>1000</v>
       </c>
-      <c r="H30" s="19"/>
-      <c r="I30" s="13" t="s">
+      <c r="H30" s="20"/>
+      <c r="I30" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K30" s="13" t="s">
+      <c r="J30" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K30" s="14" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:11" outlineLevel="2">
       <c r="A31" s="5"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="14" t="s">
+      <c r="B31" s="10"/>
+      <c r="C31" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="17" t="s">
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G31" s="14">
         <v>1000</v>
       </c>
-      <c r="H31" s="17" t="s">
+      <c r="H31" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="I31" s="13" t="s">
+      <c r="I31" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K31" s="13" t="s">
+      <c r="J31" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K31" s="14" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:11" outlineLevel="2">
       <c r="A32" s="5"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="14" t="s">
+      <c r="B32" s="10"/>
+      <c r="C32" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="13">
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="14">
         <v>1000</v>
       </c>
-      <c r="H32" s="18"/>
-      <c r="I32" s="13" t="s">
+      <c r="H32" s="19"/>
+      <c r="I32" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="J32" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K32" s="13" t="s">
+      <c r="J32" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K32" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:11" outlineLevel="2">
       <c r="A33" s="5"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="14" t="s">
+      <c r="B33" s="11"/>
+      <c r="C33" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="13">
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="14">
         <v>1000</v>
       </c>
-      <c r="H33" s="19"/>
-      <c r="I33" s="13" t="s">
+      <c r="H33" s="20"/>
+      <c r="I33" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K33" s="13" t="s">
+      <c r="J33" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K33" s="14" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:11" outlineLevel="1">
       <c r="A34" s="5"/>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
     </row>
     <row r="35" spans="1:11" outlineLevel="2">
       <c r="A35" s="5"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="14" t="s">
+      <c r="B35" s="10"/>
+      <c r="C35" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13">
+      <c r="D35" s="14"/>
+      <c r="E35" s="14">
         <v>5</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="G35" s="13">
+      <c r="G35" s="14">
         <v>2000</v>
       </c>
-      <c r="H35" s="17" t="s">
+      <c r="H35" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="I35" s="13" t="s">
+      <c r="I35" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J35" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K35" s="13"/>
+      <c r="K35" s="14"/>
     </row>
     <row r="36" spans="1:11" outlineLevel="2">
       <c r="A36" s="5"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="14" t="s">
+      <c r="B36" s="10"/>
+      <c r="C36" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13">
+      <c r="D36" s="14"/>
+      <c r="E36" s="14">
         <v>6</v>
       </c>
-      <c r="F36" s="19"/>
-      <c r="G36" s="13">
+      <c r="F36" s="20"/>
+      <c r="G36" s="14">
         <v>2000</v>
       </c>
-      <c r="H36" s="19"/>
-      <c r="I36" s="13" t="s">
+      <c r="H36" s="20"/>
+      <c r="I36" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J36" s="13" t="s">
+      <c r="J36" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K36" s="13"/>
+      <c r="K36" s="14"/>
     </row>
     <row r="37" spans="1:11" outlineLevel="2">
       <c r="A37" s="5"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="14" t="s">
+      <c r="B37" s="10"/>
+      <c r="C37" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13">
+      <c r="D37" s="14"/>
+      <c r="E37" s="14">
         <v>6</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="14">
         <v>1500</v>
       </c>
-      <c r="H37" s="13" t="s">
+      <c r="H37" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="I37" s="13" t="s">
+      <c r="I37" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="J37" s="13" t="s">
+      <c r="J37" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K37" s="13"/>
+      <c r="K37" s="14"/>
     </row>
     <row r="38" spans="1:11" outlineLevel="2">
       <c r="A38" s="5"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="14" t="s">
+      <c r="B38" s="10"/>
+      <c r="C38" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13">
+      <c r="D38" s="14"/>
+      <c r="E38" s="14">
         <v>6</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="14">
         <v>1500</v>
       </c>
-      <c r="H38" s="13" t="s">
+      <c r="H38" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I38" s="13" t="s">
+      <c r="I38" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J38" s="13" t="s">
+      <c r="J38" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K38" s="13"/>
+      <c r="K38" s="14"/>
     </row>
     <row r="39" spans="1:11" outlineLevel="2">
       <c r="A39" s="5"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="14" t="s">
+      <c r="B39" s="10"/>
+      <c r="C39" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13">
+      <c r="D39" s="14"/>
+      <c r="E39" s="14">
         <v>6</v>
       </c>
-      <c r="F39" s="13" t="s">
+      <c r="F39" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="G39" s="13">
+      <c r="G39" s="14">
         <v>2000</v>
       </c>
-      <c r="H39" s="13" t="s">
+      <c r="H39" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I39" s="13" t="s">
+      <c r="I39" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J39" s="13" t="s">
+      <c r="J39" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K39" s="13"/>
+      <c r="K39" s="14"/>
     </row>
     <row r="40" spans="1:11" outlineLevel="2">
       <c r="A40" s="5"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="14" t="s">
+      <c r="B40" s="10"/>
+      <c r="C40" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13">
+      <c r="D40" s="14"/>
+      <c r="E40" s="14">
         <v>4</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F40" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="G40" s="13">
+      <c r="G40" s="14">
         <v>1500</v>
       </c>
-      <c r="H40" s="13" t="s">
+      <c r="H40" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I40" s="13" t="s">
+      <c r="I40" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="J40" s="13" t="s">
+      <c r="J40" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K40" s="13"/>
+      <c r="K40" s="14"/>
     </row>
     <row r="41" spans="1:11" outlineLevel="2">
       <c r="A41" s="5"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
     </row>
     <row r="42" spans="1:11" outlineLevel="1">
       <c r="A42" s="5"/>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
     </row>
     <row r="43" spans="1:11" outlineLevel="2">
       <c r="A43" s="5"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="14" t="s">
+      <c r="B43" s="10"/>
+      <c r="C43" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13">
+      <c r="D43" s="14"/>
+      <c r="E43" s="14">
         <v>8</v>
       </c>
-      <c r="F43" s="13" t="s">
+      <c r="F43" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="G43" s="13">
+      <c r="G43" s="14">
         <v>1000</v>
       </c>
-      <c r="H43" s="13" t="s">
+      <c r="H43" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I43" s="13" t="s">
+      <c r="I43" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J43" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K43" s="13"/>
+      <c r="J43" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K43" s="14"/>
     </row>
     <row r="44" spans="1:11" outlineLevel="2">
       <c r="A44" s="5"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="14" t="s">
+      <c r="B44" s="10"/>
+      <c r="C44" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13">
+      <c r="D44" s="14"/>
+      <c r="E44" s="14">
         <v>8</v>
       </c>
-      <c r="F44" s="13" t="s">
+      <c r="F44" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="G44" s="13">
+      <c r="G44" s="14">
         <v>1000</v>
       </c>
-      <c r="H44" s="13" t="s">
+      <c r="H44" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I44" s="13" t="s">
+      <c r="I44" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J44" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K44" s="13"/>
+      <c r="J44" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K44" s="14"/>
     </row>
     <row r="45" spans="1:11" outlineLevel="2">
       <c r="A45" s="5"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="14" t="s">
+      <c r="B45" s="10"/>
+      <c r="C45" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13">
+      <c r="D45" s="14"/>
+      <c r="E45" s="14">
         <v>8</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="G45" s="13">
+      <c r="G45" s="14">
         <v>1000</v>
       </c>
-      <c r="H45" s="13" t="s">
+      <c r="H45" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I45" s="13" t="s">
+      <c r="I45" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J45" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K45" s="13"/>
+      <c r="J45" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K45" s="14"/>
     </row>
     <row r="46" spans="1:11" outlineLevel="1">
       <c r="A46" s="5"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
     </row>
     <row r="47" spans="1:11" outlineLevel="1">
       <c r="A47" s="6"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="14"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
     </row>
     <row r="49" spans="1:11" outlineLevel="1">
       <c r="A49" s="5"/>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C49" s="14"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
     </row>
     <row r="50" spans="1:11" outlineLevel="2">
       <c r="A50" s="5"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="14" t="s">
+      <c r="B50" s="10"/>
+      <c r="C50" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13">
+      <c r="D50" s="14"/>
+      <c r="E50" s="14">
         <v>5</v>
       </c>
-      <c r="F50" s="13" t="s">
+      <c r="F50" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G50" s="13">
+      <c r="G50" s="14">
         <v>5000</v>
       </c>
-      <c r="H50" s="13" t="s">
+      <c r="H50" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="I50" s="13" t="s">
+      <c r="I50" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J50" s="13" t="s">
+      <c r="J50" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="K50" s="13"/>
+      <c r="K50" s="14"/>
     </row>
     <row r="51" spans="1:11" outlineLevel="2">
       <c r="A51" s="5"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="14" t="s">
+      <c r="B51" s="10"/>
+      <c r="C51" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13">
+      <c r="D51" s="14"/>
+      <c r="E51" s="14">
         <v>5</v>
       </c>
-      <c r="F51" s="13" t="s">
+      <c r="F51" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G51" s="13">
+      <c r="G51" s="14">
         <v>3000</v>
       </c>
-      <c r="H51" s="13" t="s">
+      <c r="H51" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="I51" s="13" t="s">
+      <c r="I51" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J51" s="13" t="s">
+      <c r="J51" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="K51" s="13"/>
+      <c r="K51" s="14"/>
     </row>
     <row r="52" spans="1:11" outlineLevel="2">
       <c r="A52" s="5"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="14" t="s">
+      <c r="B52" s="10"/>
+      <c r="C52" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13">
+      <c r="D52" s="14"/>
+      <c r="E52" s="14">
         <v>5</v>
       </c>
-      <c r="F52" s="13" t="s">
+      <c r="F52" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G52" s="13">
+      <c r="G52" s="14">
         <v>3000</v>
       </c>
-      <c r="H52" s="13" t="s">
+      <c r="H52" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="I52" s="13" t="s">
+      <c r="I52" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J52" s="13" t="s">
+      <c r="J52" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="K52" s="13"/>
+      <c r="K52" s="14"/>
     </row>
     <row r="53" spans="1:11" outlineLevel="2">
       <c r="A53" s="5"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="14" t="s">
+      <c r="B53" s="10"/>
+      <c r="C53" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13">
+      <c r="D53" s="14"/>
+      <c r="E53" s="14">
         <v>5</v>
       </c>
-      <c r="F53" s="13" t="s">
+      <c r="F53" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G53" s="13">
+      <c r="G53" s="14">
         <v>2000</v>
       </c>
-      <c r="H53" s="13" t="s">
+      <c r="H53" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="I53" s="13" t="s">
+      <c r="I53" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J53" s="13" t="s">
+      <c r="J53" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="K53" s="13"/>
+      <c r="K53" s="14"/>
     </row>
     <row r="54" spans="1:11" outlineLevel="2">
       <c r="A54" s="5"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="14" t="s">
+      <c r="B54" s="11"/>
+      <c r="C54" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13">
+      <c r="D54" s="14"/>
+      <c r="E54" s="14">
         <v>5</v>
       </c>
-      <c r="F54" s="13" t="s">
+      <c r="F54" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G54" s="13">
+      <c r="G54" s="14">
         <v>2000</v>
       </c>
-      <c r="H54" s="13" t="s">
+      <c r="H54" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="I54" s="13" t="s">
+      <c r="I54" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J54" s="13" t="s">
+      <c r="J54" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="K54" s="13"/>
+      <c r="K54" s="14"/>
     </row>
     <row r="55" spans="1:11" outlineLevel="1">
       <c r="A55" s="5"/>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="14"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="K55" s="13"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
     </row>
     <row r="56" spans="1:11" outlineLevel="2">
       <c r="A56" s="5"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="14" t="s">
+      <c r="B56" s="10"/>
+      <c r="C56" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13">
+      <c r="D56" s="14"/>
+      <c r="E56" s="14">
         <v>5</v>
       </c>
-      <c r="F56" s="13" t="s">
+      <c r="F56" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G56" s="13">
+      <c r="G56" s="14">
         <v>1000</v>
       </c>
-      <c r="H56" s="13" t="s">
+      <c r="H56" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I56" s="13" t="s">
+      <c r="I56" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J56" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K56" s="13"/>
+      <c r="J56" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K56" s="14"/>
     </row>
     <row r="57" spans="1:11" outlineLevel="2">
       <c r="A57" s="5"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="14" t="s">
+      <c r="B57" s="10"/>
+      <c r="C57" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13">
+      <c r="D57" s="14"/>
+      <c r="E57" s="14">
         <v>5</v>
       </c>
-      <c r="F57" s="13" t="s">
+      <c r="F57" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G57" s="13">
+      <c r="G57" s="14">
         <v>1000</v>
       </c>
-      <c r="H57" s="13" t="s">
+      <c r="H57" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I57" s="13" t="s">
+      <c r="I57" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J57" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K57" s="13"/>
+      <c r="J57" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K57" s="14"/>
     </row>
     <row r="58" spans="1:11" outlineLevel="2">
       <c r="A58" s="5"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="14" t="s">
+      <c r="B58" s="10"/>
+      <c r="C58" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13">
+      <c r="D58" s="14"/>
+      <c r="E58" s="14">
         <v>3</v>
       </c>
-      <c r="F58" s="13" t="s">
+      <c r="F58" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G58" s="13">
+      <c r="G58" s="14">
         <v>1000</v>
       </c>
-      <c r="H58" s="13" t="s">
+      <c r="H58" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I58" s="13" t="s">
+      <c r="I58" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J58" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K58" s="13"/>
+      <c r="J58" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K58" s="14"/>
     </row>
     <row r="59" spans="1:11" outlineLevel="2">
       <c r="A59" s="5"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="14" t="s">
+      <c r="B59" s="11"/>
+      <c r="C59" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13">
+      <c r="D59" s="14"/>
+      <c r="E59" s="14">
         <v>1</v>
       </c>
-      <c r="F59" s="13" t="s">
+      <c r="F59" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G59" s="13">
+      <c r="G59" s="14">
         <v>1000</v>
       </c>
-      <c r="H59" s="13" t="s">
+      <c r="H59" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I59" s="13" t="s">
+      <c r="I59" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J59" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K59" s="13"/>
+      <c r="J59" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K59" s="14"/>
     </row>
     <row r="60" spans="1:11" outlineLevel="1">
       <c r="A60" s="5"/>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C60" s="14"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
     </row>
     <row r="61" spans="1:11" outlineLevel="2">
       <c r="A61" s="5"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="14" t="s">
+      <c r="B61" s="10"/>
+      <c r="C61" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13">
+      <c r="D61" s="14"/>
+      <c r="E61" s="14">
         <v>6</v>
       </c>
-      <c r="F61" s="13" t="s">
+      <c r="F61" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G61" s="13">
+      <c r="G61" s="14">
         <v>1000</v>
       </c>
-      <c r="H61" s="13" t="s">
+      <c r="H61" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I61" s="13" t="s">
+      <c r="I61" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J61" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K61" s="13"/>
+      <c r="J61" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K61" s="14"/>
     </row>
     <row r="62" spans="1:11" outlineLevel="2">
       <c r="A62" s="5"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="14" t="s">
+      <c r="B62" s="10"/>
+      <c r="C62" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13">
+      <c r="D62" s="14"/>
+      <c r="E62" s="14">
         <v>5</v>
       </c>
-      <c r="F62" s="13" t="s">
+      <c r="F62" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="G62" s="13">
+      <c r="G62" s="14">
         <v>1000</v>
       </c>
-      <c r="H62" s="13" t="s">
+      <c r="H62" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I62" s="13" t="s">
+      <c r="I62" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J62" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K62" s="13"/>
+      <c r="J62" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K62" s="14"/>
     </row>
     <row r="63" spans="1:11" outlineLevel="2">
       <c r="A63" s="5"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="14" t="s">
+      <c r="B63" s="10"/>
+      <c r="C63" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13">
+      <c r="D63" s="14"/>
+      <c r="E63" s="14">
         <v>6</v>
       </c>
-      <c r="F63" s="13" t="s">
+      <c r="F63" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="G63" s="13">
+      <c r="G63" s="14">
         <v>1000</v>
       </c>
-      <c r="H63" s="13" t="s">
+      <c r="H63" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I63" s="13" t="s">
+      <c r="I63" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J63" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K63" s="13"/>
+      <c r="J63" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K63" s="14"/>
     </row>
     <row r="64" spans="1:11" outlineLevel="2">
       <c r="A64" s="5"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="14" t="s">
+      <c r="B64" s="10"/>
+      <c r="C64" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13">
+      <c r="D64" s="14"/>
+      <c r="E64" s="14">
         <v>6</v>
       </c>
-      <c r="F64" s="13" t="s">
+      <c r="F64" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="G64" s="13">
+      <c r="G64" s="14">
         <v>1000</v>
       </c>
-      <c r="H64" s="13" t="s">
+      <c r="H64" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I64" s="13" t="s">
+      <c r="I64" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J64" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K64" s="13"/>
+      <c r="J64" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K64" s="14"/>
     </row>
     <row r="65" spans="1:11" outlineLevel="2">
       <c r="A65" s="5"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="14" t="s">
+      <c r="B65" s="10"/>
+      <c r="C65" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13">
+      <c r="D65" s="14"/>
+      <c r="E65" s="14">
         <v>5</v>
       </c>
-      <c r="F65" s="13" t="s">
+      <c r="F65" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="G65" s="13">
+      <c r="G65" s="14">
         <v>1000</v>
       </c>
-      <c r="H65" s="13" t="s">
+      <c r="H65" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I65" s="13" t="s">
+      <c r="I65" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J65" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K65" s="13"/>
+      <c r="J65" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K65" s="14"/>
     </row>
     <row r="66" spans="1:11" outlineLevel="2">
       <c r="A66" s="5"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13"/>
-      <c r="K66" s="13"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="14"/>
     </row>
     <row r="67" spans="1:11" outlineLevel="1">
       <c r="A67" s="5"/>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C67" s="14"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="13"/>
-      <c r="K67" s="13"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="14"/>
     </row>
     <row r="68" spans="1:11" outlineLevel="2">
       <c r="A68" s="5"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="14" t="s">
+      <c r="B68" s="10"/>
+      <c r="C68" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13">
+      <c r="D68" s="14"/>
+      <c r="E68" s="14">
         <v>5</v>
       </c>
-      <c r="F68" s="17" t="s">
+      <c r="F68" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="G68" s="13">
+      <c r="G68" s="14">
         <v>2000</v>
       </c>
-      <c r="H68" s="13" t="s">
+      <c r="H68" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="I68" s="13" t="s">
+      <c r="I68" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J68" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K68" s="13"/>
+      <c r="J68" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K68" s="14"/>
     </row>
     <row r="69" spans="1:11" outlineLevel="2">
       <c r="A69" s="5"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="14" t="s">
+      <c r="B69" s="10"/>
+      <c r="C69" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13">
+      <c r="D69" s="14"/>
+      <c r="E69" s="14">
         <v>5</v>
       </c>
-      <c r="F69" s="18"/>
-      <c r="G69" s="13">
+      <c r="F69" s="19"/>
+      <c r="G69" s="14">
         <v>2000</v>
       </c>
-      <c r="H69" s="13" t="s">
+      <c r="H69" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="I69" s="13" t="s">
+      <c r="I69" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J69" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K69" s="13"/>
+      <c r="J69" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K69" s="14"/>
     </row>
     <row r="70" spans="1:11" outlineLevel="2">
       <c r="A70" s="5"/>
-      <c r="B70" s="10"/>
-      <c r="C70" s="14" t="s">
+      <c r="B70" s="11"/>
+      <c r="C70" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13">
+      <c r="D70" s="14"/>
+      <c r="E70" s="14">
         <v>4</v>
       </c>
-      <c r="F70" s="19"/>
-      <c r="G70" s="13">
+      <c r="F70" s="20"/>
+      <c r="G70" s="14">
         <v>1000</v>
       </c>
-      <c r="H70" s="13" t="s">
+      <c r="H70" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="I70" s="13" t="s">
+      <c r="I70" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J70" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K70" s="13"/>
+      <c r="J70" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K70" s="14"/>
     </row>
     <row r="71" spans="1:11" outlineLevel="1">
       <c r="A71" s="5"/>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C71" s="14"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="13"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
     </row>
     <row r="72" spans="1:11" outlineLevel="2">
       <c r="A72" s="5"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="14" t="s">
+      <c r="B72" s="10"/>
+      <c r="C72" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13">
+      <c r="D72" s="14"/>
+      <c r="E72" s="14">
         <v>5</v>
       </c>
-      <c r="F72" s="17" t="s">
+      <c r="F72" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="G72" s="13">
+      <c r="G72" s="14">
         <v>2000</v>
       </c>
-      <c r="H72" s="17" t="s">
+      <c r="H72" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="I72" s="13" t="s">
+      <c r="I72" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J72" s="13" t="s">
+      <c r="J72" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="K72" s="13"/>
+      <c r="K72" s="14"/>
     </row>
     <row r="73" spans="1:11" outlineLevel="2">
       <c r="A73" s="5"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="14" t="s">
+      <c r="B73" s="10"/>
+      <c r="C73" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13">
+      <c r="D73" s="14"/>
+      <c r="E73" s="14">
         <v>4</v>
       </c>
-      <c r="F73" s="18"/>
-      <c r="G73" s="13">
+      <c r="F73" s="19"/>
+      <c r="G73" s="14">
         <v>1000</v>
       </c>
-      <c r="H73" s="18"/>
-      <c r="I73" s="13" t="s">
+      <c r="H73" s="19"/>
+      <c r="I73" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J73" s="13" t="s">
+      <c r="J73" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="K73" s="13"/>
+      <c r="K73" s="14"/>
     </row>
     <row r="74" spans="1:11" outlineLevel="2">
       <c r="A74" s="5"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="14" t="s">
+      <c r="B74" s="10"/>
+      <c r="C74" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13">
+      <c r="D74" s="14"/>
+      <c r="E74" s="14">
         <v>5</v>
       </c>
-      <c r="F74" s="18"/>
-      <c r="G74" s="13">
+      <c r="F74" s="19"/>
+      <c r="G74" s="14">
         <v>2000</v>
       </c>
-      <c r="H74" s="18"/>
-      <c r="I74" s="13" t="s">
+      <c r="H74" s="19"/>
+      <c r="I74" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J74" s="13" t="s">
+      <c r="J74" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="K74" s="13"/>
+      <c r="K74" s="14"/>
     </row>
     <row r="75" spans="1:11" outlineLevel="2">
       <c r="A75" s="5"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="14" t="s">
+      <c r="B75" s="10"/>
+      <c r="C75" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13">
+      <c r="D75" s="14"/>
+      <c r="E75" s="14">
         <v>5</v>
       </c>
-      <c r="F75" s="19"/>
-      <c r="G75" s="13">
+      <c r="F75" s="20"/>
+      <c r="G75" s="14">
         <v>3000</v>
       </c>
-      <c r="H75" s="19"/>
-      <c r="I75" s="13" t="s">
+      <c r="H75" s="20"/>
+      <c r="I75" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J75" s="13" t="s">
+      <c r="J75" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="K75" s="13"/>
+      <c r="K75" s="14"/>
     </row>
     <row r="76" spans="1:11" ht="27" outlineLevel="2">
       <c r="A76" s="5"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="14" t="s">
+      <c r="B76" s="10"/>
+      <c r="C76" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="D76" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="E76" s="13">
+      <c r="E76" s="14">
         <v>3</v>
       </c>
-      <c r="F76" s="13" t="s">
+      <c r="F76" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="G76" s="13">
+      <c r="G76" s="14">
         <v>1000</v>
       </c>
-      <c r="H76" s="13" t="s">
+      <c r="H76" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I76" s="13" t="s">
+      <c r="I76" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J76" s="13" t="s">
+      <c r="J76" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="K76" s="13"/>
+      <c r="K76" s="14"/>
     </row>
     <row r="77" spans="1:11" outlineLevel="2">
       <c r="A77" s="5"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="14" t="s">
+      <c r="B77" s="10"/>
+      <c r="C77" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13">
+      <c r="D77" s="14"/>
+      <c r="E77" s="14">
         <v>3</v>
       </c>
-      <c r="F77" s="13" t="s">
+      <c r="F77" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="G77" s="13">
+      <c r="G77" s="14">
         <v>1000</v>
       </c>
-      <c r="H77" s="13" t="s">
+      <c r="H77" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="I77" s="13" t="s">
+      <c r="I77" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="J77" s="13" t="s">
+      <c r="J77" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="K77" s="13"/>
+      <c r="K77" s="14"/>
     </row>
     <row r="78" spans="1:11" outlineLevel="2">
       <c r="A78" s="5"/>
-      <c r="B78" s="10"/>
-      <c r="C78" s="14" t="s">
+      <c r="B78" s="11"/>
+      <c r="C78" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13">
+      <c r="D78" s="14"/>
+      <c r="E78" s="14">
         <v>5</v>
       </c>
-      <c r="F78" s="13" t="s">
+      <c r="F78" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G78" s="13">
+      <c r="G78" s="14">
         <v>3000</v>
       </c>
-      <c r="H78" s="13" t="s">
+      <c r="H78" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="I78" s="13" t="s">
+      <c r="I78" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="J78" s="13" t="s">
+      <c r="J78" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="K78" s="13"/>
+      <c r="K78" s="14"/>
     </row>
     <row r="79" spans="1:11" outlineLevel="1">
       <c r="A79" s="5"/>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C79" s="14"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
-      <c r="J79" s="13"/>
-      <c r="K79" s="13"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="23"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="14"/>
     </row>
     <row r="80" spans="1:11" outlineLevel="2">
       <c r="A80" s="5"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="14" t="s">
+      <c r="B80" s="10"/>
+      <c r="C80" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13">
+      <c r="D80" s="14"/>
+      <c r="E80" s="14">
         <v>5</v>
       </c>
-      <c r="F80" s="13" t="s">
+      <c r="F80" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="G80" s="13">
+      <c r="G80" s="14">
         <v>2000</v>
       </c>
-      <c r="H80" s="13" t="s">
+      <c r="H80" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="I80" s="13" t="s">
+      <c r="I80" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J80" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K80" s="13"/>
+      <c r="J80" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K80" s="14"/>
     </row>
     <row r="81" spans="1:11" outlineLevel="2">
       <c r="A81" s="5"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="14" t="s">
+      <c r="B81" s="10"/>
+      <c r="C81" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13">
+      <c r="D81" s="14"/>
+      <c r="E81" s="14">
         <v>5</v>
       </c>
-      <c r="F81" s="13" t="s">
+      <c r="F81" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="G81" s="13">
+      <c r="G81" s="14">
         <v>1500</v>
       </c>
-      <c r="H81" s="13" t="s">
+      <c r="H81" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="I81" s="13" t="s">
+      <c r="I81" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J81" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K81" s="13"/>
+      <c r="J81" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K81" s="14"/>
     </row>
     <row r="82" spans="1:11" outlineLevel="2">
       <c r="A82" s="5"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="14" t="s">
+      <c r="B82" s="10"/>
+      <c r="C82" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13">
+      <c r="D82" s="14"/>
+      <c r="E82" s="14">
         <v>3</v>
       </c>
-      <c r="F82" s="13" t="s">
+      <c r="F82" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="G82" s="13">
+      <c r="G82" s="14">
         <v>3000</v>
       </c>
-      <c r="H82" s="13" t="s">
+      <c r="H82" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="I82" s="13" t="s">
+      <c r="I82" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J82" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K82" s="13"/>
+      <c r="J82" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K82" s="14"/>
     </row>
     <row r="83" spans="1:11" outlineLevel="2">
       <c r="A83" s="5"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="14" t="s">
+      <c r="B83" s="10"/>
+      <c r="C83" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13">
+      <c r="D83" s="14"/>
+      <c r="E83" s="14">
         <v>6</v>
       </c>
-      <c r="F83" s="13" t="s">
+      <c r="F83" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="G83" s="13">
+      <c r="G83" s="14">
         <v>5000</v>
       </c>
-      <c r="H83" s="13" t="s">
+      <c r="H83" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I83" s="13" t="s">
+      <c r="I83" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="J83" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K83" s="13"/>
+      <c r="J83" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K83" s="14"/>
     </row>
     <row r="84" spans="1:11" outlineLevel="2">
       <c r="A84" s="5"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="14" t="s">
+      <c r="B84" s="10"/>
+      <c r="C84" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13">
+      <c r="D84" s="14"/>
+      <c r="E84" s="14">
         <v>6</v>
       </c>
-      <c r="F84" s="13" t="s">
+      <c r="F84" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="G84" s="13">
+      <c r="G84" s="14">
         <v>3000</v>
       </c>
-      <c r="H84" s="13" t="s">
+      <c r="H84" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I84" s="13" t="s">
+      <c r="I84" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J84" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K84" s="13"/>
+      <c r="J84" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K84" s="14"/>
     </row>
     <row r="85" spans="1:11" outlineLevel="2">
       <c r="A85" s="5"/>
-      <c r="B85" s="10"/>
-      <c r="C85" s="14" t="s">
+      <c r="B85" s="11"/>
+      <c r="C85" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13">
+      <c r="D85" s="14"/>
+      <c r="E85" s="14">
         <v>4</v>
       </c>
-      <c r="F85" s="13" t="s">
+      <c r="F85" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G85" s="13">
+      <c r="G85" s="14">
         <v>1000</v>
       </c>
-      <c r="H85" s="13" t="s">
+      <c r="H85" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I85" s="13" t="s">
+      <c r="I85" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J85" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K85" s="13"/>
+      <c r="J85" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K85" s="14"/>
     </row>
     <row r="86" spans="1:11" ht="11.25" customHeight="1" outlineLevel="1">
       <c r="A86" s="5"/>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C86" s="14"/>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="13"/>
-      <c r="J86" s="13"/>
-      <c r="K86" s="13"/>
+      <c r="C86" s="15"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+      <c r="K86" s="14"/>
     </row>
     <row r="87" spans="1:11" outlineLevel="2">
       <c r="A87" s="5"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="14" t="s">
+      <c r="B87" s="10"/>
+      <c r="C87" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13">
+      <c r="D87" s="14"/>
+      <c r="E87" s="14">
         <v>5</v>
       </c>
-      <c r="F87" s="13" t="s">
+      <c r="F87" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G87" s="13">
+      <c r="G87" s="14">
         <v>2000</v>
       </c>
-      <c r="H87" s="13" t="s">
+      <c r="H87" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I87" s="13" t="s">
+      <c r="I87" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J87" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K87" s="13"/>
+      <c r="J87" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K87" s="14"/>
     </row>
     <row r="88" spans="1:11" outlineLevel="2">
       <c r="A88" s="5"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="14" t="s">
+      <c r="B88" s="10"/>
+      <c r="C88" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13">
+      <c r="D88" s="14"/>
+      <c r="E88" s="14">
         <v>5</v>
       </c>
-      <c r="F88" s="13" t="s">
+      <c r="F88" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G88" s="13">
+      <c r="G88" s="14">
         <v>2000</v>
       </c>
-      <c r="H88" s="13" t="s">
+      <c r="H88" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I88" s="13" t="s">
+      <c r="I88" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J88" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K88" s="13"/>
+      <c r="J88" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K88" s="14"/>
     </row>
     <row r="89" spans="1:11" outlineLevel="2">
       <c r="A89" s="5"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="14" t="s">
+      <c r="B89" s="10"/>
+      <c r="C89" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13">
+      <c r="D89" s="14"/>
+      <c r="E89" s="14">
         <v>5</v>
       </c>
-      <c r="F89" s="13" t="s">
+      <c r="F89" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G89" s="13">
+      <c r="G89" s="14">
         <v>1000</v>
       </c>
-      <c r="H89" s="13" t="s">
+      <c r="H89" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I89" s="13" t="s">
+      <c r="I89" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="J89" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K89" s="13"/>
+      <c r="J89" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K89" s="14"/>
     </row>
     <row r="90" spans="1:11" outlineLevel="2">
       <c r="A90" s="5"/>
-      <c r="B90" s="10"/>
-      <c r="C90" s="14" t="s">
+      <c r="B90" s="11"/>
+      <c r="C90" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13">
+      <c r="D90" s="14"/>
+      <c r="E90" s="14">
         <v>5</v>
       </c>
-      <c r="F90" s="13" t="s">
+      <c r="F90" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G90" s="13">
+      <c r="G90" s="14">
         <v>2000</v>
       </c>
-      <c r="H90" s="13" t="s">
+      <c r="H90" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="I90" s="13" t="s">
+      <c r="I90" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="J90" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K90" s="13"/>
+      <c r="J90" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K90" s="14"/>
     </row>
     <row r="91" spans="1:11" outlineLevel="1">
       <c r="A91" s="5"/>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="C91" s="14"/>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="13"/>
-      <c r="H91" s="13"/>
-      <c r="I91" s="13"/>
-      <c r="J91" s="13"/>
-      <c r="K91" s="13"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+      <c r="K91" s="14"/>
     </row>
     <row r="92" spans="1:11" outlineLevel="2">
       <c r="A92" s="5"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="14" t="s">
+      <c r="B92" s="10"/>
+      <c r="C92" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="D92" s="13"/>
-      <c r="E92" s="13">
+      <c r="D92" s="14"/>
+      <c r="E92" s="14">
         <v>5</v>
       </c>
-      <c r="F92" s="13" t="s">
+      <c r="F92" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G92" s="13">
+      <c r="G92" s="14">
         <v>1000</v>
       </c>
-      <c r="H92" s="13" t="s">
+      <c r="H92" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I92" s="13" t="s">
+      <c r="I92" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J92" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K92" s="13"/>
+      <c r="J92" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K92" s="14"/>
     </row>
     <row r="93" spans="1:11" outlineLevel="2">
       <c r="A93" s="5"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="14" t="s">
+      <c r="B93" s="10"/>
+      <c r="C93" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13">
+      <c r="D93" s="14"/>
+      <c r="E93" s="14">
         <v>5</v>
       </c>
-      <c r="F93" s="13" t="s">
+      <c r="F93" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G93" s="13">
+      <c r="G93" s="14">
         <v>1000</v>
       </c>
-      <c r="H93" s="13" t="s">
+      <c r="H93" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I93" s="13" t="s">
+      <c r="I93" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J93" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K93" s="13"/>
+      <c r="J93" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K93" s="14"/>
     </row>
     <row r="94" spans="1:11" outlineLevel="2">
       <c r="A94" s="5"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="14" t="s">
+      <c r="B94" s="10"/>
+      <c r="C94" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13">
+      <c r="D94" s="14"/>
+      <c r="E94" s="14">
         <v>5</v>
       </c>
-      <c r="F94" s="13" t="s">
+      <c r="F94" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G94" s="13">
+      <c r="G94" s="14">
         <v>1000</v>
       </c>
-      <c r="H94" s="13" t="s">
+      <c r="H94" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I94" s="13" t="s">
+      <c r="I94" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J94" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K94" s="13"/>
+      <c r="J94" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K94" s="14"/>
     </row>
     <row r="95" spans="1:11" outlineLevel="2">
       <c r="A95" s="5"/>
-      <c r="B95" s="10"/>
-      <c r="C95" s="14" t="s">
+      <c r="B95" s="11"/>
+      <c r="C95" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13">
+      <c r="D95" s="14"/>
+      <c r="E95" s="14">
         <v>5</v>
       </c>
-      <c r="F95" s="13" t="s">
+      <c r="F95" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G95" s="13">
+      <c r="G95" s="14">
         <v>1000</v>
       </c>
-      <c r="H95" s="13" t="s">
+      <c r="H95" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="I95" s="13" t="s">
+      <c r="I95" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J95" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K95" s="13"/>
+      <c r="J95" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K95" s="14"/>
     </row>
     <row r="96" spans="1:11" outlineLevel="1">
       <c r="A96" s="5"/>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C96" s="14"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
-      <c r="I96" s="13"/>
-      <c r="J96" s="13"/>
-      <c r="K96" s="13"/>
+      <c r="C96" s="15"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="14"/>
+      <c r="K96" s="14"/>
     </row>
     <row r="97" spans="1:11" outlineLevel="2">
       <c r="A97" s="5"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="14" t="s">
+      <c r="B97" s="10"/>
+      <c r="C97" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="D97" s="13"/>
-      <c r="E97" s="13">
+      <c r="D97" s="14"/>
+      <c r="E97" s="14">
         <v>4</v>
       </c>
-      <c r="F97" s="13" t="s">
+      <c r="F97" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G97" s="13">
+      <c r="G97" s="14">
         <v>1000</v>
       </c>
-      <c r="H97" s="13" t="s">
+      <c r="H97" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I97" s="13" t="s">
+      <c r="I97" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J97" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K97" s="13"/>
+      <c r="J97" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K97" s="14"/>
     </row>
     <row r="98" spans="1:11" outlineLevel="2">
       <c r="A98" s="5"/>
-      <c r="B98" s="10"/>
-      <c r="C98" s="14" t="s">
+      <c r="B98" s="11"/>
+      <c r="C98" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13">
+      <c r="D98" s="14"/>
+      <c r="E98" s="14">
         <v>4</v>
       </c>
-      <c r="F98" s="13" t="s">
+      <c r="F98" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G98" s="13">
+      <c r="G98" s="14">
         <v>1000</v>
       </c>
-      <c r="H98" s="13" t="s">
+      <c r="H98" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="I98" s="13" t="s">
+      <c r="I98" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="J98" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K98" s="13"/>
+      <c r="J98" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K98" s="14"/>
     </row>
     <row r="99" spans="1:11" outlineLevel="1">
       <c r="A99" s="5"/>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C99" s="14"/>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
-      <c r="H99" s="13"/>
-      <c r="I99" s="13"/>
-      <c r="J99" s="13"/>
-      <c r="K99" s="13"/>
+      <c r="C99" s="15"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="14"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="14"/>
+      <c r="H99" s="14"/>
+      <c r="I99" s="14"/>
+      <c r="J99" s="14"/>
+      <c r="K99" s="14"/>
     </row>
     <row r="100" spans="1:11" outlineLevel="2">
       <c r="A100" s="5"/>
-      <c r="B100" s="9"/>
-      <c r="C100" s="14" t="s">
+      <c r="B100" s="10"/>
+      <c r="C100" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13">
+      <c r="D100" s="14"/>
+      <c r="E100" s="14">
         <v>4</v>
       </c>
-      <c r="F100" s="17" t="s">
+      <c r="F100" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="G100" s="13">
+      <c r="G100" s="14">
         <v>1000</v>
       </c>
-      <c r="H100" s="17" t="s">
+      <c r="H100" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="I100" s="13" t="s">
+      <c r="I100" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J100" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K100" s="13"/>
+      <c r="J100" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K100" s="14"/>
     </row>
     <row r="101" spans="1:11" outlineLevel="2">
       <c r="A101" s="5"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="14" t="s">
+      <c r="B101" s="10"/>
+      <c r="C101" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="D101" s="13"/>
-      <c r="E101" s="13">
+      <c r="D101" s="14"/>
+      <c r="E101" s="14">
         <v>4</v>
       </c>
-      <c r="F101" s="18"/>
-      <c r="G101" s="13">
+      <c r="F101" s="19"/>
+      <c r="G101" s="14">
         <v>1000</v>
       </c>
-      <c r="H101" s="18"/>
-      <c r="I101" s="13" t="s">
+      <c r="H101" s="19"/>
+      <c r="I101" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J101" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K101" s="13"/>
+      <c r="J101" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K101" s="14"/>
     </row>
     <row r="102" spans="1:11" outlineLevel="2">
       <c r="A102" s="6"/>
-      <c r="B102" s="10"/>
-      <c r="C102" s="14" t="s">
+      <c r="B102" s="11"/>
+      <c r="C102" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13">
+      <c r="D102" s="14"/>
+      <c r="E102" s="14">
         <v>4</v>
       </c>
-      <c r="F102" s="19"/>
-      <c r="G102" s="13">
+      <c r="F102" s="20"/>
+      <c r="G102" s="14">
         <v>5000</v>
       </c>
-      <c r="H102" s="19"/>
-      <c r="I102" s="13" t="s">
+      <c r="H102" s="20"/>
+      <c r="I102" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J102" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K102" s="13"/>
+      <c r="J102" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K102" s="14"/>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="4" t="s">
@@ -3804,318 +3855,318 @@
       <c r="B103" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C103" s="14"/>
-      <c r="D103" s="13"/>
-      <c r="E103" s="13"/>
-      <c r="F103" s="13"/>
-      <c r="G103" s="13"/>
-      <c r="H103" s="13"/>
-      <c r="I103" s="13"/>
-      <c r="J103" s="13"/>
-      <c r="K103" s="13"/>
+      <c r="C103" s="15"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="14"/>
+      <c r="F103" s="14"/>
+      <c r="G103" s="14"/>
+      <c r="H103" s="14"/>
+      <c r="I103" s="14"/>
+      <c r="J103" s="14"/>
+      <c r="K103" s="14"/>
     </row>
     <row r="104" spans="1:11" outlineLevel="1">
       <c r="A104" s="5"/>
-      <c r="B104" s="11" t="s">
+      <c r="B104" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C104" s="14"/>
-      <c r="D104" s="13"/>
-      <c r="E104" s="13">
+      <c r="C104" s="15"/>
+      <c r="D104" s="14"/>
+      <c r="E104" s="14">
         <v>7</v>
       </c>
-      <c r="F104" s="13" t="s">
+      <c r="F104" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G104" s="13">
+      <c r="G104" s="14">
         <v>5000</v>
       </c>
-      <c r="H104" s="13" t="s">
+      <c r="H104" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="I104" s="13" t="s">
+      <c r="I104" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J104" s="13" t="s">
+      <c r="J104" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K104" s="13"/>
+      <c r="K104" s="14"/>
     </row>
     <row r="105" spans="1:11" outlineLevel="1">
       <c r="A105" s="5"/>
-      <c r="B105" s="9" t="s">
+      <c r="B105" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C105" s="14"/>
-      <c r="D105" s="13"/>
-      <c r="E105" s="13">
+      <c r="C105" s="15"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="14">
         <v>7</v>
       </c>
-      <c r="F105" s="13" t="s">
+      <c r="F105" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G105" s="13">
+      <c r="G105" s="14">
         <v>5000</v>
       </c>
-      <c r="H105" s="13" t="s">
+      <c r="H105" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="I105" s="13" t="s">
+      <c r="I105" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J105" s="13" t="s">
+      <c r="J105" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K105" s="13"/>
+      <c r="K105" s="14"/>
     </row>
     <row r="106" spans="1:11" outlineLevel="1">
       <c r="A106" s="5"/>
-      <c r="B106" s="9" t="s">
+      <c r="B106" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C106" s="14"/>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13">
+      <c r="C106" s="15"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="14">
         <v>7</v>
       </c>
-      <c r="F106" s="13" t="s">
+      <c r="F106" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G106" s="13">
+      <c r="G106" s="14">
         <v>5000</v>
       </c>
-      <c r="H106" s="13" t="s">
+      <c r="H106" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="I106" s="13" t="s">
+      <c r="I106" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J106" s="13" t="s">
+      <c r="J106" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K106" s="13"/>
+      <c r="K106" s="14"/>
     </row>
     <row r="107" spans="1:11" outlineLevel="1">
       <c r="A107" s="5"/>
-      <c r="B107" s="9" t="s">
+      <c r="B107" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C107" s="14"/>
-      <c r="D107" s="13"/>
-      <c r="E107" s="13">
+      <c r="C107" s="15"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="14">
         <v>7</v>
       </c>
-      <c r="F107" s="13" t="s">
+      <c r="F107" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G107" s="13">
+      <c r="G107" s="14">
         <v>5000</v>
       </c>
-      <c r="H107" s="13" t="s">
+      <c r="H107" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="I107" s="13" t="s">
+      <c r="I107" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="J107" s="13" t="s">
+      <c r="J107" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="K107" s="13"/>
+      <c r="K107" s="14"/>
     </row>
     <row r="108" spans="1:11" outlineLevel="1">
       <c r="A108" s="6"/>
-      <c r="B108" s="10"/>
-      <c r="C108" s="14"/>
-      <c r="D108" s="13"/>
-      <c r="E108" s="13"/>
-      <c r="F108" s="13"/>
-      <c r="G108" s="13"/>
-      <c r="H108" s="13"/>
-      <c r="I108" s="13"/>
-      <c r="J108" s="13"/>
-      <c r="K108" s="13"/>
+      <c r="B108" s="11"/>
+      <c r="C108" s="15"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="14"/>
+      <c r="F108" s="14"/>
+      <c r="G108" s="14"/>
+      <c r="H108" s="14"/>
+      <c r="I108" s="14"/>
+      <c r="J108" s="14"/>
+      <c r="K108" s="14"/>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C109" s="14"/>
-      <c r="D109" s="13"/>
-      <c r="E109" s="13"/>
-      <c r="F109" s="13"/>
-      <c r="G109" s="13"/>
-      <c r="H109" s="13"/>
-      <c r="I109" s="13"/>
-      <c r="J109" s="13"/>
-      <c r="K109" s="13"/>
+      <c r="C109" s="15"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="14"/>
+      <c r="F109" s="14"/>
+      <c r="G109" s="14"/>
+      <c r="H109" s="14"/>
+      <c r="I109" s="14"/>
+      <c r="J109" s="14"/>
+      <c r="K109" s="14"/>
     </row>
     <row r="110" spans="1:11" outlineLevel="1">
       <c r="A110" s="5"/>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="C110" s="14"/>
-      <c r="D110" s="13"/>
-      <c r="E110" s="13"/>
-      <c r="F110" s="13"/>
-      <c r="G110" s="13"/>
-      <c r="H110" s="13"/>
-      <c r="I110" s="13"/>
-      <c r="J110" s="13"/>
-      <c r="K110" s="13"/>
+      <c r="C110" s="15"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="14"/>
+      <c r="F110" s="14"/>
+      <c r="G110" s="14"/>
+      <c r="H110" s="14"/>
+      <c r="I110" s="14"/>
+      <c r="J110" s="14"/>
+      <c r="K110" s="14"/>
     </row>
     <row r="111" spans="1:11" outlineLevel="1">
       <c r="A111" s="5"/>
-      <c r="B111" s="9"/>
-      <c r="C111" s="14"/>
-      <c r="D111" s="13"/>
-      <c r="E111" s="13"/>
-      <c r="F111" s="13"/>
-      <c r="G111" s="13"/>
-      <c r="H111" s="13"/>
-      <c r="I111" s="13"/>
-      <c r="J111" s="13"/>
-      <c r="K111" s="13"/>
+      <c r="B111" s="10"/>
+      <c r="C111" s="15"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="14"/>
+      <c r="F111" s="14"/>
+      <c r="G111" s="14"/>
+      <c r="H111" s="14"/>
+      <c r="I111" s="14"/>
+      <c r="J111" s="14"/>
+      <c r="K111" s="14"/>
     </row>
     <row r="112" spans="1:11" outlineLevel="1">
       <c r="A112" s="5"/>
-      <c r="B112" s="9"/>
-      <c r="C112" s="14"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="13"/>
-      <c r="F112" s="13"/>
-      <c r="G112" s="13"/>
-      <c r="H112" s="13"/>
-      <c r="I112" s="13"/>
-      <c r="J112" s="13"/>
-      <c r="K112" s="13"/>
+      <c r="B112" s="10"/>
+      <c r="C112" s="15"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="14"/>
+      <c r="F112" s="14"/>
+      <c r="G112" s="14"/>
+      <c r="H112" s="14"/>
+      <c r="I112" s="14"/>
+      <c r="J112" s="14"/>
+      <c r="K112" s="14"/>
     </row>
     <row r="113" spans="1:11" outlineLevel="1">
       <c r="A113" s="6"/>
-      <c r="B113" s="10"/>
-      <c r="C113" s="14"/>
-      <c r="D113" s="13"/>
-      <c r="E113" s="13"/>
-      <c r="F113" s="13"/>
-      <c r="G113" s="13"/>
-      <c r="H113" s="13"/>
-      <c r="I113" s="13"/>
-      <c r="J113" s="13"/>
-      <c r="K113" s="13"/>
+      <c r="B113" s="11"/>
+      <c r="C113" s="15"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
+      <c r="F113" s="14"/>
+      <c r="G113" s="14"/>
+      <c r="H113" s="14"/>
+      <c r="I113" s="14"/>
+      <c r="J113" s="14"/>
+      <c r="K113" s="14"/>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C114" s="14"/>
-      <c r="D114" s="13"/>
-      <c r="E114" s="13"/>
-      <c r="F114" s="13"/>
-      <c r="G114" s="13"/>
-      <c r="H114" s="13"/>
-      <c r="I114" s="13"/>
-      <c r="J114" s="13"/>
-      <c r="K114" s="13"/>
+      <c r="C114" s="15"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="14"/>
+      <c r="F114" s="14"/>
+      <c r="G114" s="14"/>
+      <c r="H114" s="14"/>
+      <c r="I114" s="14"/>
+      <c r="J114" s="14"/>
+      <c r="K114" s="14"/>
     </row>
     <row r="115" spans="1:11" outlineLevel="1">
       <c r="A115" s="5"/>
-      <c r="B115" s="11" t="s">
+      <c r="B115" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C115" s="14"/>
-      <c r="D115" s="13"/>
-      <c r="E115" s="13"/>
-      <c r="F115" s="13"/>
-      <c r="G115" s="13"/>
-      <c r="H115" s="13"/>
-      <c r="I115" s="13"/>
-      <c r="J115" s="13"/>
-      <c r="K115" s="13"/>
+      <c r="C115" s="15"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="14"/>
+      <c r="F115" s="14"/>
+      <c r="G115" s="14"/>
+      <c r="H115" s="14"/>
+      <c r="I115" s="14"/>
+      <c r="J115" s="14"/>
+      <c r="K115" s="14"/>
     </row>
     <row r="116" spans="1:11" outlineLevel="1">
       <c r="A116" s="5"/>
-      <c r="B116" s="9"/>
-      <c r="C116" s="14" t="s">
+      <c r="B116" s="10"/>
+      <c r="C116" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="D116" s="13"/>
-      <c r="E116" s="13"/>
-      <c r="F116" s="13"/>
-      <c r="G116" s="13"/>
-      <c r="H116" s="13"/>
-      <c r="I116" s="13"/>
-      <c r="J116" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K116" s="13"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="14"/>
+      <c r="F116" s="14"/>
+      <c r="G116" s="14"/>
+      <c r="H116" s="14"/>
+      <c r="I116" s="14"/>
+      <c r="J116" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K116" s="14"/>
     </row>
     <row r="117" spans="1:11" outlineLevel="1">
       <c r="A117" s="5"/>
-      <c r="B117" s="9"/>
-      <c r="C117" s="16" t="s">
+      <c r="B117" s="10"/>
+      <c r="C117" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D117" s="13"/>
-      <c r="E117" s="13"/>
-      <c r="F117" s="13"/>
-      <c r="G117" s="13"/>
-      <c r="H117" s="13"/>
-      <c r="I117" s="13"/>
-      <c r="J117" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K117" s="13"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="14"/>
+      <c r="F117" s="14"/>
+      <c r="G117" s="14"/>
+      <c r="H117" s="14"/>
+      <c r="I117" s="14"/>
+      <c r="J117" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K117" s="14"/>
     </row>
     <row r="118" spans="1:11" outlineLevel="1">
       <c r="A118" s="5"/>
-      <c r="B118" s="9"/>
-      <c r="C118" s="16" t="s">
+      <c r="B118" s="10"/>
+      <c r="C118" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="D118" s="13"/>
-      <c r="E118" s="13"/>
-      <c r="F118" s="13"/>
-      <c r="G118" s="13"/>
-      <c r="H118" s="13"/>
-      <c r="I118" s="13"/>
-      <c r="J118" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K118" s="13"/>
+      <c r="D118" s="14"/>
+      <c r="E118" s="14"/>
+      <c r="F118" s="14"/>
+      <c r="G118" s="14"/>
+      <c r="H118" s="14"/>
+      <c r="I118" s="14"/>
+      <c r="J118" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K118" s="14"/>
     </row>
     <row r="119" spans="1:11" outlineLevel="1">
       <c r="A119" s="5"/>
-      <c r="B119" s="9"/>
-      <c r="C119" s="16" t="s">
+      <c r="B119" s="10"/>
+      <c r="C119" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D119" s="13"/>
-      <c r="E119" s="13"/>
-      <c r="F119" s="13"/>
-      <c r="G119" s="13"/>
-      <c r="H119" s="13"/>
-      <c r="I119" s="13"/>
-      <c r="J119" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K119" s="13"/>
+      <c r="D119" s="14"/>
+      <c r="E119" s="14"/>
+      <c r="F119" s="14"/>
+      <c r="G119" s="14"/>
+      <c r="H119" s="14"/>
+      <c r="I119" s="14"/>
+      <c r="J119" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K119" s="14"/>
     </row>
     <row r="120" spans="1:11" outlineLevel="1">
       <c r="A120" s="6"/>
-      <c r="B120" s="10"/>
-      <c r="C120" s="16" t="s">
+      <c r="B120" s="11"/>
+      <c r="C120" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
-      <c r="F120" s="13"/>
-      <c r="G120" s="13"/>
-      <c r="H120" s="13"/>
-      <c r="I120" s="13"/>
-      <c r="J120" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K120" s="13"/>
+      <c r="D120" s="14"/>
+      <c r="E120" s="14"/>
+      <c r="F120" s="14"/>
+      <c r="G120" s="14"/>
+      <c r="H120" s="14"/>
+      <c r="I120" s="14"/>
+      <c r="J120" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K120" s="14"/>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="3" t="s">
@@ -4124,29 +4175,29 @@
       <c r="B121" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C121" s="14"/>
-      <c r="D121" s="13"/>
-      <c r="E121" s="13"/>
-      <c r="F121" s="13"/>
-      <c r="G121" s="13"/>
-      <c r="H121" s="13"/>
-      <c r="I121" s="13"/>
-      <c r="J121" s="13"/>
-      <c r="K121" s="13"/>
+      <c r="C121" s="15"/>
+      <c r="D121" s="14"/>
+      <c r="E121" s="14"/>
+      <c r="F121" s="14"/>
+      <c r="G121" s="14"/>
+      <c r="H121" s="14"/>
+      <c r="I121" s="14"/>
+      <c r="J121" s="14"/>
+      <c r="K121" s="14"/>
     </row>
     <row r="122" spans="1:11">
       <c r="B122" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C122" s="14"/>
-      <c r="D122" s="13"/>
-      <c r="E122" s="13"/>
-      <c r="F122" s="13"/>
-      <c r="G122" s="13"/>
-      <c r="H122" s="13"/>
-      <c r="I122" s="13"/>
-      <c r="J122" s="13"/>
-      <c r="K122" s="13"/>
+      <c r="C122" s="15"/>
+      <c r="D122" s="14"/>
+      <c r="E122" s="14"/>
+      <c r="F122" s="14"/>
+      <c r="G122" s="14"/>
+      <c r="H122" s="14"/>
+      <c r="I122" s="14"/>
+      <c r="J122" s="14"/>
+      <c r="K122" s="14"/>
     </row>
     <row r="123" spans="1:11">
       <c r="B123" s="7" t="s">
@@ -4154,6 +4205,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K40"/>
   <dataConsolidate/>
   <mergeCells count="11">
     <mergeCell ref="F68:F70"/>
